--- a/data/reference/Unidades/plantilla_modelos_maquinarias.xlsx
+++ b/data/reference/Unidades/plantilla_modelos_maquinarias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sherrera\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tattersall-my.sharepoint.com/personal/sherrera_tattersall_cl/Documents/Escritorio/FACU/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B0ED40-AC33-4667-B411-C74549FB24E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{74B0ED40-AC33-4667-B411-C74549FB24E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC54E645-58A7-497B-A8A3-A771F9A6D71C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2459,7 +2459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2492,51 +2492,41 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE7E6E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2549,68 +2539,10 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFE7E6E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2972,8 +2904,8 @@
   <cols>
     <col min="1" max="1" width="19.85546875" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="18.5703125" style="18" customWidth="1"/>
     <col min="7" max="7" width="13.28515625" style="18" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.5703125" style="18" bestFit="1" customWidth="1"/>
@@ -2982,8 +2914,8 @@
     <col min="11" max="11" width="20.42578125" style="18" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.42578125" style="18" customWidth="1"/>
     <col min="13" max="13" width="9.140625" style="18" customWidth="1"/>
-    <col min="14" max="14" width="27.5703125" style="24" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.140625" style="18" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="18"/>
   </cols>
@@ -3074,11 +3006,14 @@
       <c r="L2" s="18" t="s">
         <v>674</v>
       </c>
-      <c r="N2" s="25">
+      <c r="M2" s="18">
+        <v>1</v>
+      </c>
+      <c r="N2">
         <f>IF(C2="","",LEN(C2))</f>
         <v>33</v>
       </c>
-      <c r="O2" s="25">
+      <c r="O2">
         <f>IF(D2="","",LEN(D2))</f>
         <v>16</v>
       </c>
@@ -3092,11 +3027,11 @@
         <f t="array" ref="D3">IF(E3="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F3)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G3)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E3)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N3" s="25" t="str">
+      <c r="N3" t="str">
         <f t="shared" ref="N3:N66" si="0">IF(C3="","",LEN(C3))</f>
         <v/>
       </c>
-      <c r="O3" s="25" t="str">
+      <c r="O3" t="str">
         <f t="shared" ref="O3:O66" si="1">IF(D3="","",LEN(D3))</f>
         <v/>
       </c>
@@ -3111,11 +3046,11 @@
         <v/>
       </c>
       <c r="E4" s="20"/>
-      <c r="N4" s="25" t="str">
+      <c r="N4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O4" s="25" t="str">
+      <c r="O4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3129,11 +3064,11 @@
         <f t="array" ref="D5">IF(E5="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F5)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G5)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E5)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N5" s="25" t="str">
+      <c r="N5" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O5" s="25" t="str">
+      <c r="O5" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3147,11 +3082,11 @@
         <f t="array" ref="D6">IF(E6="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F6)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G6)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E6)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N6" s="25" t="str">
+      <c r="N6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O6" s="25" t="str">
+      <c r="O6" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3165,11 +3100,11 @@
         <f t="array" ref="D7">IF(E7="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F7)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G7)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E7)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N7" s="25" t="str">
+      <c r="N7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O7" s="25" t="str">
+      <c r="O7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3183,11 +3118,11 @@
         <f t="array" ref="D8">IF(E8="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F8)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G8)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E8)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N8" s="25" t="str">
+      <c r="N8" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O8" s="25" t="str">
+      <c r="O8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3201,11 +3136,11 @@
         <f t="array" ref="D9">IF(E9="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F9)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G9)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E9)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N9" s="25" t="str">
+      <c r="N9" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O9" s="25" t="str">
+      <c r="O9" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3219,11 +3154,11 @@
         <f t="array" ref="D10">IF(E10="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F10)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G10)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E10)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N10" s="25" t="str">
+      <c r="N10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O10" s="25" t="str">
+      <c r="O10" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3237,11 +3172,11 @@
         <f t="array" ref="D11">IF(E11="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F11)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G11)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E11)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N11" s="25" t="str">
+      <c r="N11" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O11" s="25" t="str">
+      <c r="O11" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3255,11 +3190,11 @@
         <f t="array" ref="D12">IF(E12="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F12)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G12)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E12)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N12" s="25" t="str">
+      <c r="N12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O12" s="25" t="str">
+      <c r="O12" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3273,11 +3208,11 @@
         <f t="array" ref="D13">IF(E13="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F13)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G13)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E13)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N13" s="25" t="str">
+      <c r="N13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O13" s="25" t="str">
+      <c r="O13" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3291,11 +3226,11 @@
         <f t="array" ref="D14">IF(E14="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F14)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G14)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E14)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N14" s="25" t="str">
+      <c r="N14" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O14" s="25" t="str">
+      <c r="O14" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3309,11 +3244,11 @@
         <f t="array" ref="D15">IF(E15="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F15)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G15)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E15)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N15" s="25" t="str">
+      <c r="N15" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O15" s="25" t="str">
+      <c r="O15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3327,11 +3262,11 @@
         <f t="array" ref="D16">IF(E16="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F16)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G16)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E16)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N16" s="25" t="str">
+      <c r="N16" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O16" s="25" t="str">
+      <c r="O16" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3345,11 +3280,11 @@
         <f t="array" ref="D17">IF(E17="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F17)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G17)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E17)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N17" s="25" t="str">
+      <c r="N17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O17" s="25" t="str">
+      <c r="O17" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3363,11 +3298,11 @@
         <f t="array" ref="D18">IF(E18="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F18)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G18)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E18)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N18" s="25" t="str">
+      <c r="N18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O18" s="25" t="str">
+      <c r="O18" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3381,11 +3316,11 @@
         <f t="array" ref="D19">IF(E19="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F19)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G19)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E19)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N19" s="25" t="str">
+      <c r="N19" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O19" s="25" t="str">
+      <c r="O19" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3399,11 +3334,11 @@
         <f t="array" ref="D20">IF(E20="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F20)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G20)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E20)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N20" s="25" t="str">
+      <c r="N20" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O20" s="25" t="str">
+      <c r="O20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3417,11 +3352,11 @@
         <f t="array" ref="D21">IF(E21="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F21)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G21)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E21)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N21" s="25" t="str">
+      <c r="N21" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O21" s="25" t="str">
+      <c r="O21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3435,11 +3370,11 @@
         <f t="array" ref="D22">IF(E22="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F22)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G22)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E22)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N22" s="25" t="str">
+      <c r="N22" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O22" s="25" t="str">
+      <c r="O22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3453,11 +3388,11 @@
         <f t="array" ref="D23">IF(E23="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F23)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G23)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E23)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N23" s="25" t="str">
+      <c r="N23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O23" s="25" t="str">
+      <c r="O23" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3471,11 +3406,11 @@
         <f t="array" ref="D24">IF(E24="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F24)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G24)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E24)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N24" s="25" t="str">
+      <c r="N24" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O24" s="25" t="str">
+      <c r="O24" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3489,11 +3424,11 @@
         <f t="array" ref="D25">IF(E25="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F25)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G25)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E25)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N25" s="25" t="str">
+      <c r="N25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O25" s="25" t="str">
+      <c r="O25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3507,11 +3442,11 @@
         <f t="array" ref="D26">IF(E26="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F26)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G26)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E26)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N26" s="25" t="str">
+      <c r="N26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O26" s="25" t="str">
+      <c r="O26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3525,11 +3460,11 @@
         <f t="array" ref="D27">IF(E27="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F27)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G27)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E27)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N27" s="25" t="str">
+      <c r="N27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O27" s="25" t="str">
+      <c r="O27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3543,11 +3478,11 @@
         <f t="array" ref="D28">IF(E28="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F28)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G28)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E28)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N28" s="25" t="str">
+      <c r="N28" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O28" s="25" t="str">
+      <c r="O28" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3561,11 +3496,11 @@
         <f t="array" ref="D29">IF(E29="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F29)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G29)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E29)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N29" s="25" t="str">
+      <c r="N29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O29" s="25" t="str">
+      <c r="O29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3579,11 +3514,11 @@
         <f t="array" ref="D30">IF(E30="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F30)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G30)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E30)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N30" s="25" t="str">
+      <c r="N30" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O30" s="25" t="str">
+      <c r="O30" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3597,11 +3532,11 @@
         <f t="array" ref="D31">IF(E31="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F31)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G31)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E31)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N31" s="25" t="str">
+      <c r="N31" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O31" s="25" t="str">
+      <c r="O31" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3615,11 +3550,11 @@
         <f t="array" ref="D32">IF(E32="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F32)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G32)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E32)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N32" s="25" t="str">
+      <c r="N32" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O32" s="25" t="str">
+      <c r="O32" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3633,11 +3568,11 @@
         <f t="array" ref="D33">IF(E33="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F33)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G33)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E33)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N33" s="25" t="str">
+      <c r="N33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O33" s="25" t="str">
+      <c r="O33" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3651,11 +3586,11 @@
         <f t="array" ref="D34">IF(E34="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F34)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G34)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E34)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N34" s="25" t="str">
+      <c r="N34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O34" s="25" t="str">
+      <c r="O34" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3669,11 +3604,11 @@
         <f t="array" ref="D35">IF(E35="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F35)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G35)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E35)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N35" s="25" t="str">
+      <c r="N35" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O35" s="25" t="str">
+      <c r="O35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3687,11 +3622,11 @@
         <f t="array" ref="D36">IF(E36="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F36)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G36)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E36)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N36" s="25" t="str">
+      <c r="N36" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O36" s="25" t="str">
+      <c r="O36" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3705,11 +3640,11 @@
         <f t="array" ref="D37">IF(E37="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F37)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G37)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E37)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N37" s="25" t="str">
+      <c r="N37" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O37" s="25" t="str">
+      <c r="O37" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3723,11 +3658,11 @@
         <f t="array" ref="D38">IF(E38="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F38)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G38)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E38)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N38" s="25" t="str">
+      <c r="N38" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O38" s="25" t="str">
+      <c r="O38" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3741,11 +3676,11 @@
         <f t="array" ref="D39">IF(E39="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F39)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G39)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E39)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N39" s="25" t="str">
+      <c r="N39" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O39" s="25" t="str">
+      <c r="O39" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3759,11 +3694,11 @@
         <f t="array" ref="D40">IF(E40="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F40)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G40)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E40)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N40" s="25" t="str">
+      <c r="N40" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O40" s="25" t="str">
+      <c r="O40" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3777,11 +3712,11 @@
         <f t="array" ref="D41">IF(E41="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F41)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G41)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E41)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N41" s="25" t="str">
+      <c r="N41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O41" s="25" t="str">
+      <c r="O41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3795,11 +3730,11 @@
         <f t="array" ref="D42">IF(E42="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F42)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G42)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E42)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N42" s="25" t="str">
+      <c r="N42" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O42" s="25" t="str">
+      <c r="O42" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3813,11 +3748,11 @@
         <f t="array" ref="D43">IF(E43="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F43)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G43)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E43)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N43" s="25" t="str">
+      <c r="N43" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O43" s="25" t="str">
+      <c r="O43" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3831,11 +3766,11 @@
         <f t="array" ref="D44">IF(E44="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F44)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G44)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E44)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N44" s="25" t="str">
+      <c r="N44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O44" s="25" t="str">
+      <c r="O44" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3849,11 +3784,11 @@
         <f t="array" ref="D45">IF(E45="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F45)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G45)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E45)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N45" s="25" t="str">
+      <c r="N45" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O45" s="25" t="str">
+      <c r="O45" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3867,11 +3802,11 @@
         <f t="array" ref="D46">IF(E46="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F46)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G46)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E46)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N46" s="25" t="str">
+      <c r="N46" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O46" s="25" t="str">
+      <c r="O46" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3885,11 +3820,11 @@
         <f t="array" ref="D47">IF(E47="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F47)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G47)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E47)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N47" s="25" t="str">
+      <c r="N47" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O47" s="25" t="str">
+      <c r="O47" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3903,11 +3838,11 @@
         <f t="array" ref="D48">IF(E48="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F48)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G48)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E48)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N48" s="25" t="str">
+      <c r="N48" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O48" s="25" t="str">
+      <c r="O48" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3921,11 +3856,11 @@
         <f t="array" ref="D49">IF(E49="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F49)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G49)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E49)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N49" s="25" t="str">
+      <c r="N49" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O49" s="25" t="str">
+      <c r="O49" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3939,11 +3874,11 @@
         <f t="array" ref="D50">IF(E50="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F50)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G50)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E50)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N50" s="25" t="str">
+      <c r="N50" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O50" s="25" t="str">
+      <c r="O50" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3957,11 +3892,11 @@
         <f t="array" ref="D51">IF(E51="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F51)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G51)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E51)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N51" s="25" t="str">
+      <c r="N51" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O51" s="25" t="str">
+      <c r="O51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3975,11 +3910,11 @@
         <f t="array" ref="D52">IF(E52="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F52)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G52)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E52)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N52" s="25" t="str">
+      <c r="N52" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O52" s="25" t="str">
+      <c r="O52" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3993,11 +3928,11 @@
         <f t="array" ref="D53">IF(E53="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F53)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G53)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E53)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N53" s="25" t="str">
+      <c r="N53" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O53" s="25" t="str">
+      <c r="O53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4011,11 +3946,11 @@
         <f t="array" ref="D54">IF(E54="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F54)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G54)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E54)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N54" s="25" t="str">
+      <c r="N54" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O54" s="25" t="str">
+      <c r="O54" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4029,11 +3964,11 @@
         <f t="array" ref="D55">IF(E55="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F55)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G55)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E55)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N55" s="25" t="str">
+      <c r="N55" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O55" s="25" t="str">
+      <c r="O55" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4047,11 +3982,11 @@
         <f t="array" ref="D56">IF(E56="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F56)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G56)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E56)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N56" s="25" t="str">
+      <c r="N56" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O56" s="25" t="str">
+      <c r="O56" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4065,11 +4000,11 @@
         <f t="array" ref="D57">IF(E57="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F57)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G57)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E57)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N57" s="25" t="str">
+      <c r="N57" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O57" s="25" t="str">
+      <c r="O57" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4083,11 +4018,11 @@
         <f t="array" ref="D58">IF(E58="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F58)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G58)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E58)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N58" s="25" t="str">
+      <c r="N58" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O58" s="25" t="str">
+      <c r="O58" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4101,11 +4036,11 @@
         <f t="array" ref="D59">IF(E59="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F59)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G59)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E59)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N59" s="25" t="str">
+      <c r="N59" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O59" s="25" t="str">
+      <c r="O59" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4119,11 +4054,11 @@
         <f t="array" ref="D60">IF(E60="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F60)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G60)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E60)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N60" s="25" t="str">
+      <c r="N60" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O60" s="25" t="str">
+      <c r="O60" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4137,11 +4072,11 @@
         <f t="array" ref="D61">IF(E61="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F61)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G61)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E61)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N61" s="25" t="str">
+      <c r="N61" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O61" s="25" t="str">
+      <c r="O61" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4155,11 +4090,11 @@
         <f t="array" ref="D62">IF(E62="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F62)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G62)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E62)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N62" s="25" t="str">
+      <c r="N62" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O62" s="25" t="str">
+      <c r="O62" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4173,11 +4108,11 @@
         <f t="array" ref="D63">IF(E63="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F63)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G63)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E63)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N63" s="25" t="str">
+      <c r="N63" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O63" s="25" t="str">
+      <c r="O63" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4191,11 +4126,11 @@
         <f t="array" ref="D64">IF(E64="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F64)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G64)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E64)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N64" s="25" t="str">
+      <c r="N64" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O64" s="25" t="str">
+      <c r="O64" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4209,11 +4144,11 @@
         <f t="array" ref="D65">IF(E65="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F65)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G65)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E65)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N65" s="25" t="str">
+      <c r="N65" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O65" s="25" t="str">
+      <c r="O65" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4227,11 +4162,11 @@
         <f t="array" ref="D66">IF(E66="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F66)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G66)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E66)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N66" s="25" t="str">
+      <c r="N66" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O66" s="25" t="str">
+      <c r="O66" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4245,11 +4180,11 @@
         <f t="array" ref="D67">IF(E67="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F67)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G67)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E67)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N67" s="25" t="str">
+      <c r="N67" t="str">
         <f t="shared" ref="N67:N130" si="2">IF(C67="","",LEN(C67))</f>
         <v/>
       </c>
-      <c r="O67" s="25" t="str">
+      <c r="O67" t="str">
         <f t="shared" ref="O67:O130" si="3">IF(D67="","",LEN(D67))</f>
         <v/>
       </c>
@@ -4263,11 +4198,11 @@
         <f t="array" ref="D68">IF(E68="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F68)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G68)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E68)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N68" s="25" t="str">
+      <c r="N68" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O68" s="25" t="str">
+      <c r="O68" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4281,11 +4216,11 @@
         <f t="array" ref="D69">IF(E69="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F69)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G69)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E69)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N69" s="25" t="str">
+      <c r="N69" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O69" s="25" t="str">
+      <c r="O69" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4299,11 +4234,11 @@
         <f t="array" ref="D70">IF(E70="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F70)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G70)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E70)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N70" s="25" t="str">
+      <c r="N70" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O70" s="25" t="str">
+      <c r="O70" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4317,11 +4252,11 @@
         <f t="array" ref="D71">IF(E71="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F71)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G71)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E71)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N71" s="25" t="str">
+      <c r="N71" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O71" s="25" t="str">
+      <c r="O71" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4335,11 +4270,11 @@
         <f t="array" ref="D72">IF(E72="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F72)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G72)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E72)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N72" s="25" t="str">
+      <c r="N72" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O72" s="25" t="str">
+      <c r="O72" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4353,11 +4288,11 @@
         <f t="array" ref="D73">IF(E73="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F73)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G73)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E73)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N73" s="25" t="str">
+      <c r="N73" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O73" s="25" t="str">
+      <c r="O73" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4371,11 +4306,11 @@
         <f t="array" ref="D74">IF(E74="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F74)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G74)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E74)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N74" s="25" t="str">
+      <c r="N74" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O74" s="25" t="str">
+      <c r="O74" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4389,11 +4324,11 @@
         <f t="array" ref="D75">IF(E75="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F75)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G75)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E75)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N75" s="25" t="str">
+      <c r="N75" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O75" s="25" t="str">
+      <c r="O75" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4407,11 +4342,11 @@
         <f t="array" ref="D76">IF(E76="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F76)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G76)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E76)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N76" s="25" t="str">
+      <c r="N76" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O76" s="25" t="str">
+      <c r="O76" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4425,11 +4360,11 @@
         <f t="array" ref="D77">IF(E77="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F77)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G77)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E77)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N77" s="25" t="str">
+      <c r="N77" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O77" s="25" t="str">
+      <c r="O77" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4443,11 +4378,11 @@
         <f t="array" ref="D78">IF(E78="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F78)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G78)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E78)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N78" s="25" t="str">
+      <c r="N78" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O78" s="25" t="str">
+      <c r="O78" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4461,11 +4396,11 @@
         <f t="array" ref="D79">IF(E79="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F79)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G79)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E79)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N79" s="25" t="str">
+      <c r="N79" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O79" s="25" t="str">
+      <c r="O79" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4479,11 +4414,11 @@
         <f t="array" ref="D80">IF(E80="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F80)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G80)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E80)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N80" s="25" t="str">
+      <c r="N80" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O80" s="25" t="str">
+      <c r="O80" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4497,11 +4432,11 @@
         <f t="array" ref="D81">IF(E81="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F81)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G81)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E81)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N81" s="25" t="str">
+      <c r="N81" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O81" s="25" t="str">
+      <c r="O81" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4515,11 +4450,11 @@
         <f t="array" ref="D82">IF(E82="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F82)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G82)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E82)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N82" s="25" t="str">
+      <c r="N82" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O82" s="25" t="str">
+      <c r="O82" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4533,11 +4468,11 @@
         <f t="array" ref="D83">IF(E83="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F83)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G83)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E83)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N83" s="25" t="str">
+      <c r="N83" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O83" s="25" t="str">
+      <c r="O83" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4551,11 +4486,11 @@
         <f t="array" ref="D84">IF(E84="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F84)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G84)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E84)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N84" s="25" t="str">
+      <c r="N84" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O84" s="25" t="str">
+      <c r="O84" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4569,11 +4504,11 @@
         <f t="array" ref="D85">IF(E85="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F85)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G85)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E85)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N85" s="25" t="str">
+      <c r="N85" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O85" s="25" t="str">
+      <c r="O85" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4587,11 +4522,11 @@
         <f t="array" ref="D86">IF(E86="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F86)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G86)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E86)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N86" s="25" t="str">
+      <c r="N86" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O86" s="25" t="str">
+      <c r="O86" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4605,11 +4540,11 @@
         <f t="array" ref="D87">IF(E87="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F87)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G87)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E87)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N87" s="25" t="str">
+      <c r="N87" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O87" s="25" t="str">
+      <c r="O87" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4623,11 +4558,11 @@
         <f t="array" ref="D88">IF(E88="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F88)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G88)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E88)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N88" s="25" t="str">
+      <c r="N88" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O88" s="25" t="str">
+      <c r="O88" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4641,11 +4576,11 @@
         <f t="array" ref="D89">IF(E89="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F89)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G89)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E89)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N89" s="25" t="str">
+      <c r="N89" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O89" s="25" t="str">
+      <c r="O89" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4659,11 +4594,11 @@
         <f t="array" ref="D90">IF(E90="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F90)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G90)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E90)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N90" s="25" t="str">
+      <c r="N90" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O90" s="25" t="str">
+      <c r="O90" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4677,11 +4612,11 @@
         <f t="array" ref="D91">IF(E91="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F91)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G91)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E91)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N91" s="25" t="str">
+      <c r="N91" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O91" s="25" t="str">
+      <c r="O91" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4695,11 +4630,11 @@
         <f t="array" ref="D92">IF(E92="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F92)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G92)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E92)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N92" s="25" t="str">
+      <c r="N92" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O92" s="25" t="str">
+      <c r="O92" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4713,11 +4648,11 @@
         <f t="array" ref="D93">IF(E93="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F93)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G93)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E93)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N93" s="25" t="str">
+      <c r="N93" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O93" s="25" t="str">
+      <c r="O93" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4731,11 +4666,11 @@
         <f t="array" ref="D94">IF(E94="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F94)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G94)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E94)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N94" s="25" t="str">
+      <c r="N94" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O94" s="25" t="str">
+      <c r="O94" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4749,11 +4684,11 @@
         <f t="array" ref="D95">IF(E95="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F95)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G95)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E95)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N95" s="25" t="str">
+      <c r="N95" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O95" s="25" t="str">
+      <c r="O95" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4767,11 +4702,11 @@
         <f t="array" ref="D96">IF(E96="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F96)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G96)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E96)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N96" s="25" t="str">
+      <c r="N96" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O96" s="25" t="str">
+      <c r="O96" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4785,11 +4720,11 @@
         <f t="array" ref="D97">IF(E97="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F97)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G97)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E97)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N97" s="25" t="str">
+      <c r="N97" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O97" s="25" t="str">
+      <c r="O97" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4803,11 +4738,11 @@
         <f t="array" ref="D98">IF(E98="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F98)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G98)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E98)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N98" s="25" t="str">
+      <c r="N98" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O98" s="25" t="str">
+      <c r="O98" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4821,11 +4756,11 @@
         <f t="array" ref="D99">IF(E99="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F99)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G99)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E99)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N99" s="25" t="str">
+      <c r="N99" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O99" s="25" t="str">
+      <c r="O99" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4839,11 +4774,11 @@
         <f t="array" ref="D100">IF(E100="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F100)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G100)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E100)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N100" s="25" t="str">
+      <c r="N100" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O100" s="25" t="str">
+      <c r="O100" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4857,11 +4792,11 @@
         <f t="array" ref="D101">IF(E101="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F101)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G101)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E101)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N101" s="25" t="str">
+      <c r="N101" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O101" s="25" t="str">
+      <c r="O101" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4875,11 +4810,11 @@
         <f t="array" ref="D102">IF(E102="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F102)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G102)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E102)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N102" s="25" t="str">
+      <c r="N102" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O102" s="25" t="str">
+      <c r="O102" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4893,11 +4828,11 @@
         <f t="array" ref="D103">IF(E103="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F103)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G103)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E103)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N103" s="25" t="str">
+      <c r="N103" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O103" s="25" t="str">
+      <c r="O103" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4911,11 +4846,11 @@
         <f t="array" ref="D104">IF(E104="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F104)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G104)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E104)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N104" s="25" t="str">
+      <c r="N104" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O104" s="25" t="str">
+      <c r="O104" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4929,11 +4864,11 @@
         <f t="array" ref="D105">IF(E105="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F105)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G105)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E105)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N105" s="25" t="str">
+      <c r="N105" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O105" s="25" t="str">
+      <c r="O105" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4947,11 +4882,11 @@
         <f t="array" ref="D106">IF(E106="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F106)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G106)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E106)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N106" s="25" t="str">
+      <c r="N106" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O106" s="25" t="str">
+      <c r="O106" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4965,11 +4900,11 @@
         <f t="array" ref="D107">IF(E107="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F107)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G107)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E107)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N107" s="25" t="str">
+      <c r="N107" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O107" s="25" t="str">
+      <c r="O107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4983,11 +4918,11 @@
         <f t="array" ref="D108">IF(E108="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F108)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G108)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E108)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N108" s="25" t="str">
+      <c r="N108" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O108" s="25" t="str">
+      <c r="O108" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5001,11 +4936,11 @@
         <f t="array" ref="D109">IF(E109="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F109)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G109)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E109)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N109" s="25" t="str">
+      <c r="N109" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O109" s="25" t="str">
+      <c r="O109" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5019,11 +4954,11 @@
         <f t="array" ref="D110">IF(E110="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F110)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G110)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E110)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N110" s="25" t="str">
+      <c r="N110" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O110" s="25" t="str">
+      <c r="O110" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5037,11 +4972,11 @@
         <f t="array" ref="D111">IF(E111="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F111)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G111)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E111)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N111" s="25" t="str">
+      <c r="N111" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O111" s="25" t="str">
+      <c r="O111" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5055,11 +4990,11 @@
         <f t="array" ref="D112">IF(E112="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F112)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G112)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E112)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N112" s="25" t="str">
+      <c r="N112" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O112" s="25" t="str">
+      <c r="O112" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5073,11 +5008,11 @@
         <f t="array" ref="D113">IF(E113="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F113)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G113)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E113)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N113" s="25" t="str">
+      <c r="N113" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O113" s="25" t="str">
+      <c r="O113" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5091,11 +5026,11 @@
         <f t="array" ref="D114">IF(E114="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F114)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G114)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E114)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N114" s="25" t="str">
+      <c r="N114" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O114" s="25" t="str">
+      <c r="O114" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5109,11 +5044,11 @@
         <f t="array" ref="D115">IF(E115="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F115)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G115)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E115)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N115" s="25" t="str">
+      <c r="N115" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O115" s="25" t="str">
+      <c r="O115" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5127,11 +5062,11 @@
         <f t="array" ref="D116">IF(E116="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F116)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G116)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E116)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N116" s="25" t="str">
+      <c r="N116" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O116" s="25" t="str">
+      <c r="O116" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5145,11 +5080,11 @@
         <f t="array" ref="D117">IF(E117="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F117)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G117)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E117)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N117" s="25" t="str">
+      <c r="N117" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O117" s="25" t="str">
+      <c r="O117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5163,11 +5098,11 @@
         <f t="array" ref="D118">IF(E118="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F118)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G118)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E118)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N118" s="25" t="str">
+      <c r="N118" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O118" s="25" t="str">
+      <c r="O118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5181,11 +5116,11 @@
         <f t="array" ref="D119">IF(E119="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F119)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G119)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E119)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N119" s="25" t="str">
+      <c r="N119" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O119" s="25" t="str">
+      <c r="O119" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5199,11 +5134,11 @@
         <f t="array" ref="D120">IF(E120="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F120)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G120)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E120)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N120" s="25" t="str">
+      <c r="N120" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O120" s="25" t="str">
+      <c r="O120" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5217,11 +5152,11 @@
         <f t="array" ref="D121">IF(E121="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F121)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G121)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E121)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N121" s="25" t="str">
+      <c r="N121" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O121" s="25" t="str">
+      <c r="O121" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5235,11 +5170,11 @@
         <f t="array" ref="D122">IF(E122="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F122)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G122)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E122)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N122" s="25" t="str">
+      <c r="N122" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O122" s="25" t="str">
+      <c r="O122" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5253,11 +5188,11 @@
         <f t="array" ref="D123">IF(E123="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F123)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G123)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E123)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N123" s="25" t="str">
+      <c r="N123" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O123" s="25" t="str">
+      <c r="O123" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5271,11 +5206,11 @@
         <f t="array" ref="D124">IF(E124="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F124)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G124)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E124)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N124" s="25" t="str">
+      <c r="N124" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O124" s="25" t="str">
+      <c r="O124" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5289,11 +5224,11 @@
         <f t="array" ref="D125">IF(E125="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F125)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G125)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E125)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N125" s="25" t="str">
+      <c r="N125" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O125" s="25" t="str">
+      <c r="O125" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5307,11 +5242,11 @@
         <f t="array" ref="D126">IF(E126="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F126)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G126)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E126)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N126" s="25" t="str">
+      <c r="N126" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O126" s="25" t="str">
+      <c r="O126" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5325,11 +5260,11 @@
         <f t="array" ref="D127">IF(E127="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F127)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G127)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E127)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N127" s="25" t="str">
+      <c r="N127" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O127" s="25" t="str">
+      <c r="O127" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5343,11 +5278,11 @@
         <f t="array" ref="D128">IF(E128="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F128)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G128)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E128)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N128" s="25" t="str">
+      <c r="N128" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O128" s="25" t="str">
+      <c r="O128" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5361,11 +5296,11 @@
         <f t="array" ref="D129">IF(E129="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F129)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G129)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E129)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N129" s="25" t="str">
+      <c r="N129" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O129" s="25" t="str">
+      <c r="O129" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5379,11 +5314,11 @@
         <f t="array" ref="D130">IF(E130="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F130)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G130)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E130)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N130" s="25" t="str">
+      <c r="N130" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O130" s="25" t="str">
+      <c r="O130" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5397,11 +5332,11 @@
         <f t="array" ref="D131">IF(E131="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F131)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G131)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E131)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N131" s="25" t="str">
+      <c r="N131" t="str">
         <f t="shared" ref="N131:N194" si="4">IF(C131="","",LEN(C131))</f>
         <v/>
       </c>
-      <c r="O131" s="25" t="str">
+      <c r="O131" t="str">
         <f t="shared" ref="O131:O194" si="5">IF(D131="","",LEN(D131))</f>
         <v/>
       </c>
@@ -5415,11 +5350,11 @@
         <f t="array" ref="D132">IF(E132="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F132)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G132)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E132)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N132" s="25" t="str">
+      <c r="N132" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O132" s="25" t="str">
+      <c r="O132" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5433,11 +5368,11 @@
         <f t="array" ref="D133">IF(E133="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F133)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G133)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E133)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N133" s="25" t="str">
+      <c r="N133" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O133" s="25" t="str">
+      <c r="O133" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5451,11 +5386,11 @@
         <f t="array" ref="D134">IF(E134="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F134)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G134)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E134)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N134" s="25" t="str">
+      <c r="N134" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O134" s="25" t="str">
+      <c r="O134" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5469,11 +5404,11 @@
         <f t="array" ref="D135">IF(E135="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F135)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G135)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E135)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N135" s="25" t="str">
+      <c r="N135" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O135" s="25" t="str">
+      <c r="O135" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5487,11 +5422,11 @@
         <f t="array" ref="D136">IF(E136="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F136)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G136)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E136)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N136" s="25" t="str">
+      <c r="N136" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O136" s="25" t="str">
+      <c r="O136" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5505,11 +5440,11 @@
         <f t="array" ref="D137">IF(E137="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F137)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G137)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E137)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N137" s="25" t="str">
+      <c r="N137" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O137" s="25" t="str">
+      <c r="O137" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5523,11 +5458,11 @@
         <f t="array" ref="D138">IF(E138="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F138)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G138)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E138)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N138" s="25" t="str">
+      <c r="N138" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O138" s="25" t="str">
+      <c r="O138" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5541,11 +5476,11 @@
         <f t="array" ref="D139">IF(E139="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F139)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G139)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E139)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N139" s="25" t="str">
+      <c r="N139" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O139" s="25" t="str">
+      <c r="O139" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5559,11 +5494,11 @@
         <f t="array" ref="D140">IF(E140="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F140)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G140)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E140)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N140" s="25" t="str">
+      <c r="N140" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O140" s="25" t="str">
+      <c r="O140" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5577,11 +5512,11 @@
         <f t="array" ref="D141">IF(E141="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F141)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G141)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E141)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N141" s="25" t="str">
+      <c r="N141" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O141" s="25" t="str">
+      <c r="O141" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5595,11 +5530,11 @@
         <f t="array" ref="D142">IF(E142="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F142)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G142)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E142)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N142" s="25" t="str">
+      <c r="N142" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O142" s="25" t="str">
+      <c r="O142" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5613,11 +5548,11 @@
         <f t="array" ref="D143">IF(E143="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F143)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G143)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E143)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N143" s="25" t="str">
+      <c r="N143" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O143" s="25" t="str">
+      <c r="O143" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5631,11 +5566,11 @@
         <f t="array" ref="D144">IF(E144="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F144)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G144)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E144)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N144" s="25" t="str">
+      <c r="N144" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O144" s="25" t="str">
+      <c r="O144" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5649,11 +5584,11 @@
         <f t="array" ref="D145">IF(E145="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F145)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G145)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E145)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N145" s="25" t="str">
+      <c r="N145" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O145" s="25" t="str">
+      <c r="O145" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5667,11 +5602,11 @@
         <f t="array" ref="D146">IF(E146="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F146)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G146)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E146)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N146" s="25" t="str">
+      <c r="N146" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O146" s="25" t="str">
+      <c r="O146" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5685,11 +5620,11 @@
         <f t="array" ref="D147">IF(E147="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F147)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G147)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E147)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N147" s="25" t="str">
+      <c r="N147" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O147" s="25" t="str">
+      <c r="O147" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5703,11 +5638,11 @@
         <f t="array" ref="D148">IF(E148="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F148)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G148)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E148)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N148" s="25" t="str">
+      <c r="N148" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O148" s="25" t="str">
+      <c r="O148" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5721,11 +5656,11 @@
         <f t="array" ref="D149">IF(E149="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F149)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G149)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E149)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N149" s="25" t="str">
+      <c r="N149" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O149" s="25" t="str">
+      <c r="O149" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5739,11 +5674,11 @@
         <f t="array" ref="D150">IF(E150="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F150)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G150)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E150)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N150" s="25" t="str">
+      <c r="N150" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O150" s="25" t="str">
+      <c r="O150" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5757,11 +5692,11 @@
         <f t="array" ref="D151">IF(E151="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F151)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G151)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E151)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N151" s="25" t="str">
+      <c r="N151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O151" s="25" t="str">
+      <c r="O151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5775,11 +5710,11 @@
         <f t="array" ref="D152">IF(E152="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F152)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G152)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E152)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N152" s="25" t="str">
+      <c r="N152" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O152" s="25" t="str">
+      <c r="O152" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5793,11 +5728,11 @@
         <f t="array" ref="D153">IF(E153="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F153)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G153)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E153)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N153" s="25" t="str">
+      <c r="N153" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O153" s="25" t="str">
+      <c r="O153" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5811,11 +5746,11 @@
         <f t="array" ref="D154">IF(E154="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F154)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G154)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E154)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N154" s="25" t="str">
+      <c r="N154" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O154" s="25" t="str">
+      <c r="O154" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5829,11 +5764,11 @@
         <f t="array" ref="D155">IF(E155="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F155)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G155)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E155)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N155" s="25" t="str">
+      <c r="N155" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O155" s="25" t="str">
+      <c r="O155" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5847,11 +5782,11 @@
         <f t="array" ref="D156">IF(E156="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F156)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G156)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E156)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N156" s="25" t="str">
+      <c r="N156" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O156" s="25" t="str">
+      <c r="O156" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5865,11 +5800,11 @@
         <f t="array" ref="D157">IF(E157="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F157)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G157)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E157)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N157" s="25" t="str">
+      <c r="N157" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O157" s="25" t="str">
+      <c r="O157" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5883,11 +5818,11 @@
         <f t="array" ref="D158">IF(E158="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F158)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G158)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E158)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N158" s="25" t="str">
+      <c r="N158" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O158" s="25" t="str">
+      <c r="O158" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5901,11 +5836,11 @@
         <f t="array" ref="D159">IF(E159="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F159)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G159)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E159)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N159" s="25" t="str">
+      <c r="N159" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O159" s="25" t="str">
+      <c r="O159" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5919,11 +5854,11 @@
         <f t="array" ref="D160">IF(E160="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F160)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G160)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E160)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N160" s="25" t="str">
+      <c r="N160" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O160" s="25" t="str">
+      <c r="O160" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5937,11 +5872,11 @@
         <f t="array" ref="D161">IF(E161="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F161)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G161)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E161)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N161" s="25" t="str">
+      <c r="N161" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O161" s="25" t="str">
+      <c r="O161" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5955,11 +5890,11 @@
         <f t="array" ref="D162">IF(E162="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F162)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G162)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E162)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N162" s="25" t="str">
+      <c r="N162" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O162" s="25" t="str">
+      <c r="O162" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5973,11 +5908,11 @@
         <f t="array" ref="D163">IF(E163="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F163)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G163)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E163)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N163" s="25" t="str">
+      <c r="N163" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O163" s="25" t="str">
+      <c r="O163" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -5991,11 +5926,11 @@
         <f t="array" ref="D164">IF(E164="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F164)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G164)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E164)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N164" s="25" t="str">
+      <c r="N164" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O164" s="25" t="str">
+      <c r="O164" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6009,11 +5944,11 @@
         <f t="array" ref="D165">IF(E165="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F165)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G165)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E165)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N165" s="25" t="str">
+      <c r="N165" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O165" s="25" t="str">
+      <c r="O165" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6027,11 +5962,11 @@
         <f t="array" ref="D166">IF(E166="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F166)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G166)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E166)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N166" s="25" t="str">
+      <c r="N166" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O166" s="25" t="str">
+      <c r="O166" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6045,11 +5980,11 @@
         <f t="array" ref="D167">IF(E167="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F167)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G167)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E167)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N167" s="25" t="str">
+      <c r="N167" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O167" s="25" t="str">
+      <c r="O167" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6063,11 +5998,11 @@
         <f t="array" ref="D168">IF(E168="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F168)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G168)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E168)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N168" s="25" t="str">
+      <c r="N168" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O168" s="25" t="str">
+      <c r="O168" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6081,11 +6016,11 @@
         <f t="array" ref="D169">IF(E169="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F169)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G169)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E169)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N169" s="25" t="str">
+      <c r="N169" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O169" s="25" t="str">
+      <c r="O169" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6099,11 +6034,11 @@
         <f t="array" ref="D170">IF(E170="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F170)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G170)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E170)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N170" s="25" t="str">
+      <c r="N170" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O170" s="25" t="str">
+      <c r="O170" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6117,11 +6052,11 @@
         <f t="array" ref="D171">IF(E171="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F171)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G171)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E171)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N171" s="25" t="str">
+      <c r="N171" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O171" s="25" t="str">
+      <c r="O171" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6135,11 +6070,11 @@
         <f t="array" ref="D172">IF(E172="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F172)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G172)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E172)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N172" s="25" t="str">
+      <c r="N172" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O172" s="25" t="str">
+      <c r="O172" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6153,11 +6088,11 @@
         <f t="array" ref="D173">IF(E173="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F173)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G173)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E173)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N173" s="25" t="str">
+      <c r="N173" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O173" s="25" t="str">
+      <c r="O173" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6171,11 +6106,11 @@
         <f t="array" ref="D174">IF(E174="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F174)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G174)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E174)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N174" s="25" t="str">
+      <c r="N174" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O174" s="25" t="str">
+      <c r="O174" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6189,11 +6124,11 @@
         <f t="array" ref="D175">IF(E175="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F175)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G175)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E175)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N175" s="25" t="str">
+      <c r="N175" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O175" s="25" t="str">
+      <c r="O175" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6207,11 +6142,11 @@
         <f t="array" ref="D176">IF(E176="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F176)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G176)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E176)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N176" s="25" t="str">
+      <c r="N176" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O176" s="25" t="str">
+      <c r="O176" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6225,11 +6160,11 @@
         <f t="array" ref="D177">IF(E177="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F177)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G177)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E177)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N177" s="25" t="str">
+      <c r="N177" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O177" s="25" t="str">
+      <c r="O177" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6243,11 +6178,11 @@
         <f t="array" ref="D178">IF(E178="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F178)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G178)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E178)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N178" s="25" t="str">
+      <c r="N178" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O178" s="25" t="str">
+      <c r="O178" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6261,11 +6196,11 @@
         <f t="array" ref="D179">IF(E179="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F179)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G179)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E179)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N179" s="25" t="str">
+      <c r="N179" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O179" s="25" t="str">
+      <c r="O179" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6279,11 +6214,11 @@
         <f t="array" ref="D180">IF(E180="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F180)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G180)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E180)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N180" s="25" t="str">
+      <c r="N180" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O180" s="25" t="str">
+      <c r="O180" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6297,11 +6232,11 @@
         <f t="array" ref="D181">IF(E181="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F181)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G181)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E181)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N181" s="25" t="str">
+      <c r="N181" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O181" s="25" t="str">
+      <c r="O181" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6315,11 +6250,11 @@
         <f t="array" ref="D182">IF(E182="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F182)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G182)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E182)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N182" s="25" t="str">
+      <c r="N182" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O182" s="25" t="str">
+      <c r="O182" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6333,11 +6268,11 @@
         <f t="array" ref="D183">IF(E183="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F183)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G183)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E183)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N183" s="25" t="str">
+      <c r="N183" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O183" s="25" t="str">
+      <c r="O183" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6351,11 +6286,11 @@
         <f t="array" ref="D184">IF(E184="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F184)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G184)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E184)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N184" s="25" t="str">
+      <c r="N184" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O184" s="25" t="str">
+      <c r="O184" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6369,11 +6304,11 @@
         <f t="array" ref="D185">IF(E185="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F185)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G185)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E185)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N185" s="25" t="str">
+      <c r="N185" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O185" s="25" t="str">
+      <c r="O185" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6387,11 +6322,11 @@
         <f t="array" ref="D186">IF(E186="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F186)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G186)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E186)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N186" s="25" t="str">
+      <c r="N186" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O186" s="25" t="str">
+      <c r="O186" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6405,11 +6340,11 @@
         <f t="array" ref="D187">IF(E187="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F187)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G187)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E187)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N187" s="25" t="str">
+      <c r="N187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O187" s="25" t="str">
+      <c r="O187" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6423,11 +6358,11 @@
         <f t="array" ref="D188">IF(E188="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F188)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G188)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E188)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N188" s="25" t="str">
+      <c r="N188" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O188" s="25" t="str">
+      <c r="O188" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6441,11 +6376,11 @@
         <f t="array" ref="D189">IF(E189="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F189)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G189)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E189)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N189" s="25" t="str">
+      <c r="N189" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O189" s="25" t="str">
+      <c r="O189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6459,11 +6394,11 @@
         <f t="array" ref="D190">IF(E190="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F190)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G190)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E190)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N190" s="25" t="str">
+      <c r="N190" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O190" s="25" t="str">
+      <c r="O190" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6477,11 +6412,11 @@
         <f t="array" ref="D191">IF(E191="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F191)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G191)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E191)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N191" s="25" t="str">
+      <c r="N191" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O191" s="25" t="str">
+      <c r="O191" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6495,11 +6430,11 @@
         <f t="array" ref="D192">IF(E192="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F192)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G192)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E192)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N192" s="25" t="str">
+      <c r="N192" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O192" s="25" t="str">
+      <c r="O192" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6513,11 +6448,11 @@
         <f t="array" ref="D193">IF(E193="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F193)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G193)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E193)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N193" s="25" t="str">
+      <c r="N193" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O193" s="25" t="str">
+      <c r="O193" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6531,11 +6466,11 @@
         <f t="array" ref="D194">IF(E194="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F194)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G194)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E194)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N194" s="25" t="str">
+      <c r="N194" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O194" s="25" t="str">
+      <c r="O194" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6549,11 +6484,11 @@
         <f t="array" ref="D195">IF(E195="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F195)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G195)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E195)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N195" s="25" t="str">
+      <c r="N195" t="str">
         <f t="shared" ref="N195:N200" si="6">IF(C195="","",LEN(C195))</f>
         <v/>
       </c>
-      <c r="O195" s="25" t="str">
+      <c r="O195" t="str">
         <f t="shared" ref="O195:O200" si="7">IF(D195="","",LEN(D195))</f>
         <v/>
       </c>
@@ -6567,11 +6502,11 @@
         <f t="array" ref="D196">IF(E196="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F196)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G196)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E196)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N196" s="25" t="str">
+      <c r="N196" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O196" s="25" t="str">
+      <c r="O196" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6585,11 +6520,11 @@
         <f t="array" ref="D197">IF(E197="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F197)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G197)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E197)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N197" s="25" t="str">
+      <c r="N197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O197" s="25" t="str">
+      <c r="O197" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6603,11 +6538,11 @@
         <f t="array" ref="D198">IF(E198="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F198)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G198)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E198)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N198" s="25" t="str">
+      <c r="N198" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O198" s="25" t="str">
+      <c r="O198" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6621,11 +6556,11 @@
         <f t="array" ref="D199">IF(E199="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F199)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G199)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E199)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N199" s="25" t="str">
+      <c r="N199" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O199" s="25" t="str">
+      <c r="O199" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6639,11 +6574,11 @@
         <f t="array" ref="D200">IF(E200="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F200)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G200)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E200)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
-      <c r="N200" s="25" t="str">
+      <c r="N200" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O200" s="25" t="str">
+      <c r="O200" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6651,12 +6586,12 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" insertRows="0" autoFilter="0"/>
   <conditionalFormatting sqref="C2:C200">
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>LEN(C2)&gt;40</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D200">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>LEN(D2)&gt;30</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6665,14 +6600,14 @@
       <formula>AND(ISNUMBER(N2),N2&gt;40)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O200">
-    <cfRule type="expression" dxfId="1" priority="6">
-      <formula>AND(ISNUMBER(O2),O2&gt;30)</formula>
+  <conditionalFormatting sqref="N2:O200">
+    <cfRule type="expression" dxfId="1" priority="8">
+      <formula>N2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O200">
-    <cfRule type="expression" dxfId="0" priority="8">
-      <formula>N2&lt;&gt;""</formula>
+  <conditionalFormatting sqref="O2:O200">
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>AND(ISNUMBER(O2),O2&gt;30)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -6754,1017 +6689,1016 @@
   <dimension ref="A1:AG40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" style="24" customWidth="1"/>
-    <col min="2" max="2" width="12" style="24" customWidth="1"/>
-    <col min="3" max="3" width="3" style="24" customWidth="1"/>
-    <col min="4" max="4" width="22" style="24" customWidth="1"/>
-    <col min="5" max="5" width="12" style="24" customWidth="1"/>
-    <col min="6" max="6" width="3" style="24" customWidth="1"/>
-    <col min="7" max="7" width="24" style="24" customWidth="1"/>
-    <col min="8" max="8" width="14" style="24" customWidth="1"/>
-    <col min="9" max="9" width="3" style="24" customWidth="1"/>
-    <col min="10" max="10" width="10" style="24" customWidth="1"/>
-    <col min="11" max="11" width="3" style="24" customWidth="1"/>
-    <col min="12" max="12" width="14" style="24" customWidth="1"/>
-    <col min="13" max="13" width="3" style="24" customWidth="1"/>
-    <col min="14" max="15" width="22" style="24" customWidth="1"/>
-    <col min="16" max="16" width="2.42578125" style="24" customWidth="1"/>
-    <col min="17" max="17" width="24" style="24" customWidth="1"/>
-    <col min="18" max="18" width="3" style="24" customWidth="1"/>
-    <col min="19" max="19" width="28" style="24" customWidth="1"/>
-    <col min="20" max="20" width="3" style="24" customWidth="1"/>
-    <col min="21" max="21" width="12" style="24" customWidth="1"/>
-    <col min="22" max="22" width="8.7109375" style="24" customWidth="1"/>
-    <col min="23" max="23" width="22" style="24" customWidth="1"/>
-    <col min="24" max="24" width="12" style="24" customWidth="1"/>
-    <col min="25" max="25" width="40" style="24" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" style="24" customWidth="1"/>
-    <col min="27" max="27" width="24" style="24" customWidth="1"/>
-    <col min="28" max="28" width="48" style="24" customWidth="1"/>
-    <col min="29" max="29" width="34" style="24" customWidth="1"/>
-    <col min="30" max="30" width="40" style="24" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="24" customWidth="1"/>
-    <col min="32" max="32" width="43" style="24" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.7109375" style="24" customWidth="1"/>
-    <col min="35" max="16384" width="8.7109375" style="24"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="3" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="3" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="3" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="3" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="3" customWidth="1"/>
+    <col min="14" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="2.42578125" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
+    <col min="18" max="18" width="3" customWidth="1"/>
+    <col min="19" max="19" width="28" customWidth="1"/>
+    <col min="20" max="20" width="3" customWidth="1"/>
+    <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="8.7109375" customWidth="1"/>
+    <col min="23" max="23" width="22" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="40" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="27" max="27" width="24" customWidth="1"/>
+    <col min="28" max="28" width="48" customWidth="1"/>
+    <col min="29" max="29" width="34" customWidth="1"/>
+    <col min="30" max="30" width="40" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" customWidth="1"/>
+    <col min="32" max="32" width="43" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="26" t="s">
+      <c r="W1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="AA1" s="27" t="s">
+      <c r="AA1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="AF1" s="26" t="s">
+      <c r="AF1" s="24" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="W2" s="28" t="s">
+      <c r="W2" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="AA2" s="30" t="s">
+      <c r="X2" s="39"/>
+      <c r="Y2" s="39"/>
+      <c r="AA2" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="AF2" s="28" t="s">
+      <c r="AF2" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="AG2" s="29"/>
+      <c r="AG2" s="39"/>
     </row>
     <row r="3" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="31" t="s">
+      <c r="N3" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="Q3" s="31" t="s">
+      <c r="O3" s="28"/>
+      <c r="Q3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="31" t="s">
+      <c r="S3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="U3" s="31" t="s">
+      <c r="U3" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="W3" s="31" t="s">
+      <c r="W3" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="X3" s="31" t="s">
+      <c r="X3" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="Y3" s="31" t="s">
+      <c r="Y3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="AF3" s="31" t="s">
+      <c r="AF3" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="AG3" s="31" t="s">
+      <c r="AG3" s="27" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="L4" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="N4" s="34" t="s">
+      <c r="N4" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="O4" s="34" t="s">
+      <c r="O4" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="Q4" s="33" t="s">
+      <c r="Q4" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="S4" s="33" t="s">
+      <c r="S4" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="U4" s="33">
+      <c r="U4" s="29">
         <v>1</v>
       </c>
-      <c r="W4" s="35" t="s">
+      <c r="W4" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="35" t="s">
+      <c r="X4" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="Y4" s="33" t="s">
+      <c r="Y4" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="AA4" s="36" t="s">
+      <c r="AA4" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="AF4" s="35" t="s">
+      <c r="AF4" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="AG4" s="35" t="s">
+      <c r="AG4" s="31" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="L5" s="33" t="s">
+      <c r="L5" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="N5" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="34" t="s">
+      <c r="O5" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="Q5" s="33" t="s">
+      <c r="Q5" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="S5" s="33" t="s">
+      <c r="S5" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="33">
+      <c r="U5" s="29">
         <v>2</v>
       </c>
-      <c r="W5" s="35" t="s">
+      <c r="W5" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="X5" s="35" t="s">
+      <c r="X5" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="Y5" s="33" t="s">
+      <c r="Y5" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="AA5" s="31" t="s">
+      <c r="AA5" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="AB5" s="31" t="s">
+      <c r="AB5" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="AC5" s="31" t="s">
+      <c r="AC5" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="AD5" s="31" t="s">
+      <c r="AD5" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="AF5" s="35" t="s">
+      <c r="AF5" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="AG5" s="35" t="s">
+      <c r="AG5" s="31" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="33" t="s">
+      <c r="J6" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="L6" s="33" t="s">
+      <c r="L6" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="N6" s="34" t="s">
+      <c r="N6" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="O6" s="34" t="s">
+      <c r="O6" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="S6" s="33" t="s">
+      <c r="S6" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="W6" s="35" t="s">
+      <c r="W6" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="X6" s="35" t="s">
+      <c r="X6" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="Y6" s="33" t="s">
+      <c r="Y6" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="AA6" s="38" t="s">
+      <c r="AA6" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="AB6" s="38" t="s">
+      <c r="AB6" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="AC6" s="38" t="s">
+      <c r="AC6" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="AD6" s="39" t="s">
+      <c r="AD6" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="AF6" s="35" t="s">
+      <c r="AF6" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="AG6" s="35" t="s">
+      <c r="AG6" s="31" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="L7" s="33" t="s">
+      <c r="L7" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="N7" s="34" t="s">
+      <c r="N7" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="O7" s="34" t="s">
+      <c r="O7" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="S7" s="33" t="s">
+      <c r="S7" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="W7" s="35" t="s">
+      <c r="W7" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="X7" s="35" t="s">
+      <c r="X7" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="Y7" s="33" t="s">
+      <c r="Y7" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="AA7" s="38" t="s">
+      <c r="AA7" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="AB7" s="38" t="s">
+      <c r="AB7" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="AC7" s="38" t="s">
+      <c r="AC7" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="AD7" s="38" t="s">
+      <c r="AD7" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="AF7" s="35" t="s">
+      <c r="AF7" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="AG7" s="35" t="s">
+      <c r="AG7" s="31" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="G8" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="H8" s="33" t="s">
+      <c r="H8" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="N8" s="33"/>
-      <c r="O8" s="40"/>
-      <c r="S8" s="33" t="s">
+      <c r="N8" s="29"/>
+      <c r="O8" s="36"/>
+      <c r="S8" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="W8" s="35" t="s">
+      <c r="W8" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="X8" s="35" t="s">
+      <c r="X8" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="Y8" s="33" t="s">
+      <c r="Y8" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="AA8" s="39" t="s">
+      <c r="AA8" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="AB8" s="38" t="s">
+      <c r="AB8" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="AC8" s="39" t="s">
+      <c r="AC8" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="AD8" s="38" t="s">
+      <c r="AD8" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="AF8" s="35" t="s">
+      <c r="AF8" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AG8" s="35" t="s">
+      <c r="AG8" s="31" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="N9" s="33"/>
-      <c r="O9" s="40"/>
-      <c r="S9" s="33" t="s">
+      <c r="N9" s="29"/>
+      <c r="O9" s="36"/>
+      <c r="S9" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="W9" s="35" t="s">
+      <c r="W9" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="X9" s="35" t="s">
+      <c r="X9" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="Y9" s="33" t="s">
+      <c r="Y9" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="AA9" s="38" t="s">
+      <c r="AA9" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="AB9" s="38" t="s">
+      <c r="AB9" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="AC9" s="38" t="s">
+      <c r="AC9" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="AD9" s="38" t="s">
+      <c r="AD9" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="AF9" s="35" t="s">
+      <c r="AF9" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="AG9" s="35" t="s">
+      <c r="AG9" s="31" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="H10" s="33" t="s">
+      <c r="H10" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="J10" s="33" t="s">
+      <c r="J10" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="N10" s="33"/>
-      <c r="O10" s="40"/>
-      <c r="S10" s="33" t="s">
+      <c r="N10" s="29"/>
+      <c r="O10" s="36"/>
+      <c r="S10" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="W10" s="35" t="s">
+      <c r="W10" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="X10" s="35" t="s">
+      <c r="X10" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="Y10" s="33" t="s">
+      <c r="Y10" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="AA10" s="38" t="s">
+      <c r="AA10" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="AB10" s="38" t="s">
+      <c r="AB10" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="AC10" s="38" t="s">
+      <c r="AC10" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="AD10" s="38" t="s">
+      <c r="AD10" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="AF10" s="35" t="s">
+      <c r="AF10" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="AG10" s="35" t="s">
+      <c r="AG10" s="31" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="H11" s="33" t="s">
+      <c r="H11" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="S11" s="33" t="s">
+      <c r="S11" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="W11" s="35" t="s">
+      <c r="W11" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="X11" s="35" t="s">
+      <c r="X11" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="Y11" s="33" t="s">
+      <c r="Y11" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="AA11" s="38" t="s">
+      <c r="AA11" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="AB11" s="38" t="s">
+      <c r="AB11" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="AC11" s="38" t="s">
+      <c r="AC11" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="AD11" s="38" t="s">
+      <c r="AD11" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="AF11" s="35" t="s">
+      <c r="AF11" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="AG11" s="35" t="s">
+      <c r="AG11" s="31" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G12" s="33" t="s">
+      <c r="G12" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="H12" s="33" t="s">
+      <c r="H12" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="S12" s="33" t="s">
+      <c r="S12" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="W12" s="35" t="s">
+      <c r="W12" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="X12" s="35" t="s">
+      <c r="X12" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="Y12" s="33" t="s">
+      <c r="Y12" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="AA12" s="38" t="s">
+      <c r="AA12" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="AB12" s="38" t="s">
+      <c r="AB12" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="AC12" s="38" t="s">
+      <c r="AC12" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="AD12" s="38" t="s">
+      <c r="AD12" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="AF12" s="35" t="s">
+      <c r="AF12" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="AG12" s="35" t="s">
+      <c r="AG12" s="31" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="H13" s="33" t="s">
+      <c r="H13" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="S13" s="33" t="s">
+      <c r="S13" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="W13" s="35" t="s">
+      <c r="W13" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="X13" s="35" t="s">
+      <c r="X13" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="Y13" s="33" t="s">
+      <c r="Y13" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="AA13" s="38" t="s">
+      <c r="AA13" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="AB13" s="38" t="s">
+      <c r="AB13" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="AC13" s="38" t="s">
+      <c r="AC13" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="AD13" s="38" t="s">
+      <c r="AD13" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="AF13" s="35" t="s">
+      <c r="AF13" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="AG13" s="35" t="s">
+      <c r="AG13" s="31" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G14" s="33" t="s">
+      <c r="G14" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="H14" s="33" t="s">
+      <c r="H14" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="S14" s="33" t="s">
+      <c r="S14" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="W14" s="35" t="s">
+      <c r="W14" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="X14" s="35" t="s">
+      <c r="X14" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="Y14" s="33" t="s">
+      <c r="Y14" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="AF14" s="35" t="s">
+      <c r="AF14" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="AG14" s="35" t="s">
+      <c r="AG14" s="31" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G15" s="33" t="s">
+      <c r="G15" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="H15" s="33" t="s">
+      <c r="H15" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="S15" s="33" t="s">
+      <c r="S15" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="W15" s="35"/>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="33"/>
-      <c r="AA15" s="36" t="s">
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="29"/>
+      <c r="AA15" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="AF15" s="35" t="s">
+      <c r="AF15" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="AG15" s="35" t="s">
+      <c r="AG15" s="31" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="H16" s="33" t="s">
+      <c r="H16" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="S16" s="33" t="s">
+      <c r="S16" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="33"/>
-      <c r="AA16" s="41" t="s">
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="29"/>
+      <c r="AA16" s="40" t="s">
         <v>194</v>
       </c>
-      <c r="AB16" s="29"/>
-      <c r="AC16" s="29"/>
-      <c r="AD16" s="29"/>
-      <c r="AF16" s="35" t="s">
+      <c r="AB16" s="39"/>
+      <c r="AC16" s="39"/>
+      <c r="AD16" s="39"/>
+      <c r="AF16" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="AG16" s="35" t="s">
+      <c r="AG16" s="31" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="17" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="H17" s="33" t="s">
+      <c r="H17" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="S17" s="33" t="s">
+      <c r="S17" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="33"/>
-      <c r="AA17" s="41" t="s">
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="29"/>
+      <c r="AA17" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="AB17" s="29"/>
-      <c r="AC17" s="29"/>
-      <c r="AD17" s="29"/>
-      <c r="AF17" s="35"/>
-      <c r="AG17" s="35"/>
+      <c r="AB17" s="39"/>
+      <c r="AC17" s="39"/>
+      <c r="AD17" s="39"/>
+      <c r="AF17" s="31"/>
+      <c r="AG17" s="31"/>
     </row>
     <row r="18" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="H18" s="33" t="s">
+      <c r="H18" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="S18" s="33" t="s">
+      <c r="S18" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="33"/>
-      <c r="AA18" s="42" t="s">
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="29"/>
+      <c r="AA18" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="AB18" s="29"/>
-      <c r="AC18" s="29"/>
-      <c r="AD18" s="29"/>
-      <c r="AF18" s="35"/>
-      <c r="AG18" s="35"/>
+      <c r="AB18" s="39"/>
+      <c r="AC18" s="39"/>
+      <c r="AD18" s="39"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="31"/>
     </row>
     <row r="19" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="H19" s="33" t="s">
+      <c r="H19" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="S19" s="33" t="s">
+      <c r="S19" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="33"/>
-      <c r="AF19" s="35"/>
-      <c r="AG19" s="35"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="29"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="31"/>
     </row>
     <row r="20" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="H20" s="33" t="s">
+      <c r="H20" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="S20" s="33" t="s">
+      <c r="S20" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="33"/>
-      <c r="AA20" s="36" t="s">
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="29"/>
+      <c r="AA20" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="AF20" s="35"/>
-      <c r="AG20" s="35"/>
+      <c r="AF20" s="31"/>
+      <c r="AG20" s="31"/>
     </row>
     <row r="21" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G21" s="33" t="s">
+      <c r="G21" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="H21" s="33" t="s">
+      <c r="H21" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="S21" s="33" t="s">
+      <c r="S21" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="33"/>
-      <c r="AA21" s="41" t="s">
+      <c r="W21" s="31"/>
+      <c r="X21" s="31"/>
+      <c r="Y21" s="29"/>
+      <c r="AA21" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="AB21" s="29"/>
-      <c r="AC21" s="29"/>
-      <c r="AD21" s="29"/>
-      <c r="AF21" s="35"/>
-      <c r="AG21" s="35"/>
+      <c r="AB21" s="39"/>
+      <c r="AC21" s="39"/>
+      <c r="AD21" s="39"/>
+      <c r="AF21" s="31"/>
+      <c r="AG21" s="31"/>
     </row>
     <row r="22" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G22" s="33" t="s">
+      <c r="G22" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="H22" s="33" t="s">
+      <c r="H22" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="S22" s="33" t="s">
+      <c r="S22" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="33"/>
-      <c r="AA22" s="41" t="s">
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="29"/>
+      <c r="AA22" s="40" t="s">
         <v>213</v>
       </c>
-      <c r="AB22" s="29"/>
-      <c r="AC22" s="29"/>
-      <c r="AD22" s="29"/>
-      <c r="AF22" s="35"/>
-      <c r="AG22" s="35"/>
+      <c r="AB22" s="39"/>
+      <c r="AC22" s="39"/>
+      <c r="AD22" s="39"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
     </row>
     <row r="23" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G23" s="33" t="s">
+      <c r="G23" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="H23" s="33" t="s">
+      <c r="H23" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="S23" s="33" t="s">
+      <c r="S23" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="33"/>
-      <c r="AA23" s="41" t="s">
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="29"/>
+      <c r="AA23" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
-      <c r="AF23" s="35"/>
-      <c r="AG23" s="35"/>
+      <c r="AB23" s="39"/>
+      <c r="AC23" s="39"/>
+      <c r="AD23" s="39"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="31"/>
     </row>
     <row r="24" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S24" s="33" t="s">
+      <c r="S24" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="33"/>
-      <c r="AA24" s="41" t="s">
+      <c r="W24" s="31"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="29"/>
+      <c r="AA24" s="40" t="s">
         <v>217</v>
       </c>
-      <c r="AB24" s="29"/>
-      <c r="AC24" s="29"/>
-      <c r="AD24" s="29"/>
-      <c r="AF24" s="35"/>
-      <c r="AG24" s="35"/>
+      <c r="AB24" s="39"/>
+      <c r="AC24" s="39"/>
+      <c r="AD24" s="39"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="31"/>
     </row>
     <row r="25" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S25" s="33" t="s">
+      <c r="S25" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="33"/>
-      <c r="AA25" s="41" t="s">
+      <c r="W25" s="31"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="29"/>
+      <c r="AA25" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="AB25" s="29"/>
-      <c r="AC25" s="29"/>
-      <c r="AD25" s="29"/>
-      <c r="AF25" s="35"/>
-      <c r="AG25" s="35"/>
+      <c r="AB25" s="39"/>
+      <c r="AC25" s="39"/>
+      <c r="AD25" s="39"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="31"/>
     </row>
     <row r="26" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S26" s="33" t="s">
+      <c r="S26" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="33"/>
-      <c r="AA26" s="41" t="s">
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="29"/>
+      <c r="AA26" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AF26" s="35"/>
-      <c r="AG26" s="35"/>
+      <c r="AB26" s="39"/>
+      <c r="AC26" s="39"/>
+      <c r="AD26" s="39"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
     </row>
     <row r="27" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S27" s="33" t="s">
+      <c r="S27" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="33"/>
-      <c r="AA27" s="41" t="s">
+      <c r="W27" s="31"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="29"/>
+      <c r="AA27" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="29"/>
-      <c r="AF27" s="35"/>
-      <c r="AG27" s="35"/>
+      <c r="AB27" s="39"/>
+      <c r="AC27" s="39"/>
+      <c r="AD27" s="39"/>
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="31"/>
     </row>
     <row r="28" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S28" s="33" t="s">
+      <c r="S28" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="33"/>
-      <c r="AF28" s="35"/>
-      <c r="AG28" s="35"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="29"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
     </row>
     <row r="29" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S29" s="33" t="s">
+      <c r="S29" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="33"/>
-      <c r="AA29" s="43" t="s">
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="29"/>
+      <c r="AA29" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="AF29" s="35"/>
-      <c r="AG29" s="35"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="31"/>
     </row>
     <row r="30" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S30" s="33" t="s">
+      <c r="S30" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="33"/>
-      <c r="AF30" s="35"/>
-      <c r="AG30" s="35"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="31"/>
+      <c r="Y30" s="29"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="31"/>
     </row>
     <row r="31" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="33"/>
-      <c r="AF31" s="35"/>
-      <c r="AG31" s="35"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="31"/>
+      <c r="Y31" s="29"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="31"/>
     </row>
     <row r="32" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="W32" s="35"/>
-      <c r="X32" s="35"/>
-      <c r="Y32" s="33"/>
-      <c r="AF32" s="35"/>
-      <c r="AG32" s="35"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="29"/>
+      <c r="AF32" s="31"/>
+      <c r="AG32" s="31"/>
     </row>
     <row r="33" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="W33" s="35"/>
-      <c r="X33" s="35"/>
-      <c r="Y33" s="33"/>
-      <c r="AF33" s="35"/>
-      <c r="AG33" s="35"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="29"/>
+      <c r="AF33" s="31"/>
+      <c r="AG33" s="31"/>
     </row>
     <row r="34" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF34" s="35"/>
-      <c r="AG34" s="35"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="31"/>
     </row>
     <row r="35" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF35" s="35"/>
-      <c r="AG35" s="35"/>
+      <c r="AF35" s="31"/>
+      <c r="AG35" s="31"/>
     </row>
     <row r="36" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF36" s="35"/>
-      <c r="AG36" s="35"/>
+      <c r="AF36" s="31"/>
+      <c r="AG36" s="31"/>
     </row>
     <row r="37" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF37" s="35"/>
-      <c r="AG37" s="35"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="31"/>
     </row>
     <row r="38" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF38" s="35"/>
-      <c r="AG38" s="35"/>
+      <c r="AF38" s="31"/>
+      <c r="AG38" s="31"/>
     </row>
     <row r="39" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF39" s="35"/>
-      <c r="AG39" s="35"/>
+      <c r="AF39" s="31"/>
+      <c r="AG39" s="31"/>
     </row>
     <row r="40" spans="23:33" x14ac:dyDescent="0.25">
-      <c r="AF40" s="35"/>
-      <c r="AG40" s="35"/>
+      <c r="AF40" s="31"/>
+      <c r="AG40" s="31"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" autoFilter="0"/>
   <mergeCells count="12">
+    <mergeCell ref="AA27:AD27"/>
+    <mergeCell ref="AA22:AD22"/>
+    <mergeCell ref="AA26:AD26"/>
+    <mergeCell ref="AA17:AD17"/>
+    <mergeCell ref="AA18:AD18"/>
+    <mergeCell ref="AA21:AD21"/>
     <mergeCell ref="AF2:AG2"/>
     <mergeCell ref="AA24:AD24"/>
     <mergeCell ref="AA16:AD16"/>
     <mergeCell ref="AA25:AD25"/>
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="AA23:AD23"/>
-    <mergeCell ref="AA27:AD27"/>
-    <mergeCell ref="AA22:AD22"/>
-    <mergeCell ref="AA26:AD26"/>
-    <mergeCell ref="AA17:AD17"/>
-    <mergeCell ref="AA18:AD18"/>
-    <mergeCell ref="AA21:AD21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -10723,11 +10657,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F147" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F1">
-      <sortCondition ref="F1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:F147" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/reference/Unidades/plantilla_modelos_maquinarias.xlsx
+++ b/data/reference/Unidades/plantilla_modelos_maquinarias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tattersall-my.sharepoint.com/personal/sherrera_tattersall_cl/Documents/Escritorio/FACU/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{74B0ED40-AC33-4667-B411-C74549FB24E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DED16748-6DD9-4426-8B23-EAC61FDA3CD8}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{74B0ED40-AC33-4667-B411-C74549FB24E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CD3B6AD-362A-42CC-90FB-26B8407B8936}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="2025" windowWidth="20730" windowHeight="11040" tabRatio="790" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="665">
   <si>
     <t>FILIAL CODIGO</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Categorías (lista desplegable)</t>
   </si>
   <si>
-    <t>Decimales cilindrada</t>
-  </si>
-  <si>
     <t>Texto original</t>
   </si>
   <si>
@@ -202,9 +199,6 @@
     <t>Motocicleta</t>
   </si>
   <si>
-    <t>TBC</t>
-  </si>
-  <si>
     <t>HORIZON PRO</t>
   </si>
   <si>
@@ -253,9 +247,6 @@
     <t>Cuatrimoto</t>
   </si>
   <si>
-    <t>Automovil</t>
-  </si>
-  <si>
     <t>HYPER HALO</t>
   </si>
   <si>
@@ -301,9 +292,6 @@
     <t>VEHICULOS</t>
   </si>
   <si>
-    <t>Camioneta</t>
-  </si>
-  <si>
     <t>LUX PLUS XL</t>
   </si>
   <si>
@@ -355,9 +343,6 @@
     <t>USADOS</t>
   </si>
   <si>
-    <t>Comerciales</t>
-  </si>
-  <si>
     <t>LUX PLUS</t>
   </si>
   <si>
@@ -397,9 +382,6 @@
     <t>6x4</t>
   </si>
   <si>
-    <t>Station Wagon</t>
-  </si>
-  <si>
     <t>DIGNITY</t>
   </si>
   <si>
@@ -1057,15 +1039,6 @@
     <t>Unidades para maquinaria industrial (TTI, TTM, TTMQ)</t>
   </si>
   <si>
-    <t>UNID-004</t>
-  </si>
-  <si>
-    <t>MAQ. AGRICOLA</t>
-  </si>
-  <si>
-    <t>Unidades para maquinaria Agricola (TAI)</t>
-  </si>
-  <si>
     <t>Sociedad/es</t>
   </si>
   <si>
@@ -2056,13 +2029,37 @@
     <t>GSL/GLP</t>
   </si>
   <si>
-    <t>XLR8</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
     <t>TEXTO BREVE CALCULADO (MAX 40)</t>
+  </si>
+  <si>
+    <t>PASCAL</t>
+  </si>
+  <si>
+    <t>PESCAL</t>
+  </si>
+  <si>
+    <t>GRUA HORQUILLA</t>
+  </si>
+  <si>
+    <t>GRUA HOR</t>
+  </si>
+  <si>
+    <t>GRUA PORTACONTENEDOR</t>
+  </si>
+  <si>
+    <t>GRUA PORT</t>
+  </si>
+  <si>
+    <t>MAQUINA INDUSTRIAL TRACTOR</t>
+  </si>
+  <si>
+    <t>MAINDTRAC</t>
+  </si>
+  <si>
+    <t>MANIPULADOR TELESCOPICO</t>
+  </si>
+  <si>
+    <t>MANTELESC</t>
   </si>
 </sst>
 </file>
@@ -2240,7 +2237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2278,11 +2275,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2339,12 +2358,14 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2750,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="D1" s="22" t="s">
         <v>2</v>
@@ -2759,7 +2780,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="G1" s="17" t="s">
         <v>4</v>
@@ -2788,98 +2809,98 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="23" t="str" cm="1">
         <f t="array" ref="C2">IF(E2="","",_xlfn.LET(_xlpm.modelo,UPPER(TRIM(E2)),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G2)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),UPPER(TRIM(F2))&amp;" "&amp;_xlpm.modelo&amp;" "&amp;_xlpm.comb))</f>
-        <v>MINIRETROEXCAVADORA XLR8 BEV</v>
+        <v>RETROEXCAVADORA PASCAL BEV</v>
       </c>
       <c r="D2" s="23" t="str" cm="1">
-        <f t="array" ref="D2">IF(E2="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F2)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G2)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E2)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
-        <v>MINIRET-XLR8-BEV</v>
+        <f t="array" ref="D2">IF(E2="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F2)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G2)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E2)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <v>RETROEX-PASCAL-BEV</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="M2">
         <f>IF(C2="","",LEN(C2))</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N2">
         <f>IF(D2="","",LEN(D2))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="23" t="str" cm="1">
         <f t="array" ref="C3">IF(E3="","",_xlfn.LET(_xlpm.modelo,UPPER(TRIM(E3)),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G3)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),UPPER(TRIM(F3))&amp;" "&amp;_xlpm.modelo&amp;" "&amp;_xlpm.comb))</f>
-        <v>GRUA XYZ DSL</v>
+        <v>EXCAVADORA PESCAL DSL</v>
       </c>
       <c r="D3" s="23" t="str" cm="1">
-        <f t="array" ref="D3">IF(E3="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F3)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G3)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E3)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
-        <v>GRUA-XYZ-DSL</v>
+        <f t="array" ref="D3">IF(E3="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F3)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G3)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E3)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <v>EXCAV-PESCAL-DSL</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>559</v>
+        <v>386</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="M3">
         <f t="shared" ref="M3:M66" si="0">IF(C3="","",LEN(C3))</f>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N66" si="1">IF(D3="","",LEN(D3))</f>
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -2888,7 +2909,7 @@
         <v/>
       </c>
       <c r="D4" s="23" t="str" cm="1">
-        <f t="array" ref="D4">IF(E4="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F4)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G4)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E4)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D4">IF(E4="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F4)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G4)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E4)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="E4" s="20"/>
@@ -2907,7 +2928,7 @@
         <v/>
       </c>
       <c r="D5" s="23" t="str" cm="1">
-        <f t="array" ref="D5">IF(E5="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F5)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G5)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E5)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D5">IF(E5="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F5)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G5)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E5)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M5" t="str">
@@ -2925,7 +2946,7 @@
         <v/>
       </c>
       <c r="D6" s="23" t="str" cm="1">
-        <f t="array" ref="D6">IF(E6="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F6)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G6)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E6)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D6">IF(E6="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F6)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G6)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E6)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M6" t="str">
@@ -2943,7 +2964,7 @@
         <v/>
       </c>
       <c r="D7" s="23" t="str" cm="1">
-        <f t="array" ref="D7">IF(E7="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F7)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G7)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E7)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D7">IF(E7="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F7)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G7)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E7)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M7" t="str">
@@ -2961,7 +2982,7 @@
         <v/>
       </c>
       <c r="D8" s="23" t="str" cm="1">
-        <f t="array" ref="D8">IF(E8="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F8)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G8)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E8)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D8">IF(E8="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F8)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G8)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E8)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M8" t="str">
@@ -2979,7 +3000,7 @@
         <v/>
       </c>
       <c r="D9" s="23" t="str" cm="1">
-        <f t="array" ref="D9">IF(E9="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F9)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G9)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E9)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D9">IF(E9="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F9)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G9)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E9)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M9" t="str">
@@ -2997,7 +3018,7 @@
         <v/>
       </c>
       <c r="D10" s="23" t="str" cm="1">
-        <f t="array" ref="D10">IF(E10="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F10)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G10)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E10)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D10">IF(E10="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F10)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G10)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E10)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M10" t="str">
@@ -3015,7 +3036,7 @@
         <v/>
       </c>
       <c r="D11" s="23" t="str" cm="1">
-        <f t="array" ref="D11">IF(E11="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F11)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G11)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E11)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D11">IF(E11="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F11)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G11)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E11)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M11" t="str">
@@ -3033,7 +3054,7 @@
         <v/>
       </c>
       <c r="D12" s="23" t="str" cm="1">
-        <f t="array" ref="D12">IF(E12="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F12)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G12)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E12)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D12">IF(E12="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F12)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G12)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E12)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M12" t="str">
@@ -3051,7 +3072,7 @@
         <v/>
       </c>
       <c r="D13" s="23" t="str" cm="1">
-        <f t="array" ref="D13">IF(E13="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F13)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G13)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E13)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D13">IF(E13="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F13)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G13)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E13)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M13" t="str">
@@ -3069,7 +3090,7 @@
         <v/>
       </c>
       <c r="D14" s="23" t="str" cm="1">
-        <f t="array" ref="D14">IF(E14="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F14)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G14)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E14)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D14">IF(E14="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F14)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G14)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E14)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M14" t="str">
@@ -3087,7 +3108,7 @@
         <v/>
       </c>
       <c r="D15" s="23" t="str" cm="1">
-        <f t="array" ref="D15">IF(E15="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F15)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G15)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E15)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D15">IF(E15="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F15)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G15)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E15)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M15" t="str">
@@ -3105,7 +3126,7 @@
         <v/>
       </c>
       <c r="D16" s="23" t="str" cm="1">
-        <f t="array" ref="D16">IF(E16="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F16)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G16)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E16)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D16">IF(E16="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F16)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G16)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E16)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M16" t="str">
@@ -3123,7 +3144,7 @@
         <v/>
       </c>
       <c r="D17" s="23" t="str" cm="1">
-        <f t="array" ref="D17">IF(E17="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F17)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G17)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E17)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D17">IF(E17="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F17)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G17)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E17)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M17" t="str">
@@ -3141,7 +3162,7 @@
         <v/>
       </c>
       <c r="D18" s="23" t="str" cm="1">
-        <f t="array" ref="D18">IF(E18="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F18)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G18)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E18)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D18">IF(E18="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F18)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G18)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E18)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M18" t="str">
@@ -3159,7 +3180,7 @@
         <v/>
       </c>
       <c r="D19" s="23" t="str" cm="1">
-        <f t="array" ref="D19">IF(E19="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F19)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G19)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E19)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D19">IF(E19="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F19)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G19)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E19)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M19" t="str">
@@ -3177,7 +3198,7 @@
         <v/>
       </c>
       <c r="D20" s="23" t="str" cm="1">
-        <f t="array" ref="D20">IF(E20="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F20)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G20)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E20)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D20">IF(E20="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F20)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G20)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E20)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M20" t="str">
@@ -3195,7 +3216,7 @@
         <v/>
       </c>
       <c r="D21" s="23" t="str" cm="1">
-        <f t="array" ref="D21">IF(E21="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F21)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G21)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E21)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D21">IF(E21="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F21)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G21)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E21)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M21" t="str">
@@ -3213,7 +3234,7 @@
         <v/>
       </c>
       <c r="D22" s="23" t="str" cm="1">
-        <f t="array" ref="D22">IF(E22="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F22)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G22)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E22)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D22">IF(E22="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F22)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G22)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E22)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M22" t="str">
@@ -3231,7 +3252,7 @@
         <v/>
       </c>
       <c r="D23" s="23" t="str" cm="1">
-        <f t="array" ref="D23">IF(E23="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F23)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G23)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E23)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D23">IF(E23="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F23)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G23)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E23)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M23" t="str">
@@ -3249,7 +3270,7 @@
         <v/>
       </c>
       <c r="D24" s="23" t="str" cm="1">
-        <f t="array" ref="D24">IF(E24="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F24)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G24)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E24)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D24">IF(E24="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F24)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G24)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E24)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M24" t="str">
@@ -3267,7 +3288,7 @@
         <v/>
       </c>
       <c r="D25" s="23" t="str" cm="1">
-        <f t="array" ref="D25">IF(E25="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F25)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G25)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E25)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D25">IF(E25="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F25)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G25)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E25)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M25" t="str">
@@ -3285,7 +3306,7 @@
         <v/>
       </c>
       <c r="D26" s="23" t="str" cm="1">
-        <f t="array" ref="D26">IF(E26="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F26)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G26)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E26)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D26">IF(E26="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F26)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G26)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E26)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M26" t="str">
@@ -3303,7 +3324,7 @@
         <v/>
       </c>
       <c r="D27" s="23" t="str" cm="1">
-        <f t="array" ref="D27">IF(E27="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F27)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G27)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E27)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D27">IF(E27="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F27)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G27)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E27)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M27" t="str">
@@ -3321,7 +3342,7 @@
         <v/>
       </c>
       <c r="D28" s="23" t="str" cm="1">
-        <f t="array" ref="D28">IF(E28="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F28)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G28)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E28)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D28">IF(E28="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F28)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G28)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E28)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M28" t="str">
@@ -3339,7 +3360,7 @@
         <v/>
       </c>
       <c r="D29" s="23" t="str" cm="1">
-        <f t="array" ref="D29">IF(E29="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F29)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G29)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E29)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D29">IF(E29="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F29)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G29)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E29)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M29" t="str">
@@ -3357,7 +3378,7 @@
         <v/>
       </c>
       <c r="D30" s="23" t="str" cm="1">
-        <f t="array" ref="D30">IF(E30="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F30)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G30)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E30)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D30">IF(E30="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F30)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G30)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E30)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M30" t="str">
@@ -3375,7 +3396,7 @@
         <v/>
       </c>
       <c r="D31" s="23" t="str" cm="1">
-        <f t="array" ref="D31">IF(E31="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F31)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G31)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E31)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D31">IF(E31="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F31)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G31)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E31)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M31" t="str">
@@ -3393,7 +3414,7 @@
         <v/>
       </c>
       <c r="D32" s="23" t="str" cm="1">
-        <f t="array" ref="D32">IF(E32="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F32)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G32)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E32)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D32">IF(E32="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F32)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G32)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E32)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M32" t="str">
@@ -3411,7 +3432,7 @@
         <v/>
       </c>
       <c r="D33" s="23" t="str" cm="1">
-        <f t="array" ref="D33">IF(E33="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F33)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G33)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E33)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D33">IF(E33="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F33)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G33)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E33)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M33" t="str">
@@ -3429,7 +3450,7 @@
         <v/>
       </c>
       <c r="D34" s="23" t="str" cm="1">
-        <f t="array" ref="D34">IF(E34="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F34)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G34)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E34)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D34">IF(E34="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F34)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G34)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E34)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M34" t="str">
@@ -3447,7 +3468,7 @@
         <v/>
       </c>
       <c r="D35" s="23" t="str" cm="1">
-        <f t="array" ref="D35">IF(E35="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F35)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G35)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E35)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D35">IF(E35="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F35)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G35)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E35)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M35" t="str">
@@ -3465,7 +3486,7 @@
         <v/>
       </c>
       <c r="D36" s="23" t="str" cm="1">
-        <f t="array" ref="D36">IF(E36="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F36)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G36)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E36)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D36">IF(E36="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F36)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G36)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E36)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M36" t="str">
@@ -3483,7 +3504,7 @@
         <v/>
       </c>
       <c r="D37" s="23" t="str" cm="1">
-        <f t="array" ref="D37">IF(E37="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F37)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G37)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E37)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D37">IF(E37="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F37)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G37)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E37)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M37" t="str">
@@ -3501,7 +3522,7 @@
         <v/>
       </c>
       <c r="D38" s="23" t="str" cm="1">
-        <f t="array" ref="D38">IF(E38="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F38)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G38)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E38)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D38">IF(E38="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F38)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G38)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E38)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M38" t="str">
@@ -3519,7 +3540,7 @@
         <v/>
       </c>
       <c r="D39" s="23" t="str" cm="1">
-        <f t="array" ref="D39">IF(E39="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F39)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G39)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E39)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D39">IF(E39="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F39)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G39)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E39)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M39" t="str">
@@ -3537,7 +3558,7 @@
         <v/>
       </c>
       <c r="D40" s="23" t="str" cm="1">
-        <f t="array" ref="D40">IF(E40="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F40)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G40)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E40)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D40">IF(E40="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F40)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G40)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E40)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M40" t="str">
@@ -3555,7 +3576,7 @@
         <v/>
       </c>
       <c r="D41" s="23" t="str" cm="1">
-        <f t="array" ref="D41">IF(E41="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F41)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G41)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E41)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D41">IF(E41="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F41)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G41)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E41)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M41" t="str">
@@ -3573,7 +3594,7 @@
         <v/>
       </c>
       <c r="D42" s="23" t="str" cm="1">
-        <f t="array" ref="D42">IF(E42="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F42)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G42)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E42)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D42">IF(E42="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F42)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G42)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E42)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M42" t="str">
@@ -3591,7 +3612,7 @@
         <v/>
       </c>
       <c r="D43" s="23" t="str" cm="1">
-        <f t="array" ref="D43">IF(E43="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F43)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G43)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E43)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D43">IF(E43="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F43)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G43)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E43)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M43" t="str">
@@ -3609,7 +3630,7 @@
         <v/>
       </c>
       <c r="D44" s="23" t="str" cm="1">
-        <f t="array" ref="D44">IF(E44="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F44)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G44)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E44)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D44">IF(E44="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F44)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G44)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E44)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M44" t="str">
@@ -3627,7 +3648,7 @@
         <v/>
       </c>
       <c r="D45" s="23" t="str" cm="1">
-        <f t="array" ref="D45">IF(E45="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F45)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G45)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E45)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D45">IF(E45="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F45)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G45)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E45)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M45" t="str">
@@ -3645,7 +3666,7 @@
         <v/>
       </c>
       <c r="D46" s="23" t="str" cm="1">
-        <f t="array" ref="D46">IF(E46="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F46)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G46)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E46)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D46">IF(E46="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F46)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G46)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E46)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M46" t="str">
@@ -3663,7 +3684,7 @@
         <v/>
       </c>
       <c r="D47" s="23" t="str" cm="1">
-        <f t="array" ref="D47">IF(E47="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F47)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G47)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E47)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D47">IF(E47="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F47)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G47)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E47)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M47" t="str">
@@ -3681,7 +3702,7 @@
         <v/>
       </c>
       <c r="D48" s="23" t="str" cm="1">
-        <f t="array" ref="D48">IF(E48="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F48)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G48)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E48)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D48">IF(E48="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F48)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G48)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E48)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M48" t="str">
@@ -3699,7 +3720,7 @@
         <v/>
       </c>
       <c r="D49" s="23" t="str" cm="1">
-        <f t="array" ref="D49">IF(E49="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F49)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G49)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E49)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D49">IF(E49="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F49)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G49)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E49)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M49" t="str">
@@ -3717,7 +3738,7 @@
         <v/>
       </c>
       <c r="D50" s="23" t="str" cm="1">
-        <f t="array" ref="D50">IF(E50="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F50)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G50)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E50)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D50">IF(E50="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F50)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G50)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E50)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M50" t="str">
@@ -3735,7 +3756,7 @@
         <v/>
       </c>
       <c r="D51" s="23" t="str" cm="1">
-        <f t="array" ref="D51">IF(E51="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F51)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G51)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E51)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D51">IF(E51="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F51)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G51)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E51)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M51" t="str">
@@ -3753,7 +3774,7 @@
         <v/>
       </c>
       <c r="D52" s="23" t="str" cm="1">
-        <f t="array" ref="D52">IF(E52="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F52)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G52)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E52)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D52">IF(E52="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F52)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G52)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E52)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M52" t="str">
@@ -3771,7 +3792,7 @@
         <v/>
       </c>
       <c r="D53" s="23" t="str" cm="1">
-        <f t="array" ref="D53">IF(E53="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F53)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G53)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E53)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D53">IF(E53="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F53)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G53)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E53)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M53" t="str">
@@ -3789,7 +3810,7 @@
         <v/>
       </c>
       <c r="D54" s="23" t="str" cm="1">
-        <f t="array" ref="D54">IF(E54="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F54)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G54)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E54)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D54">IF(E54="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F54)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G54)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E54)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M54" t="str">
@@ -3807,7 +3828,7 @@
         <v/>
       </c>
       <c r="D55" s="23" t="str" cm="1">
-        <f t="array" ref="D55">IF(E55="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F55)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G55)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E55)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D55">IF(E55="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F55)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G55)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E55)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M55" t="str">
@@ -3825,7 +3846,7 @@
         <v/>
       </c>
       <c r="D56" s="23" t="str" cm="1">
-        <f t="array" ref="D56">IF(E56="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F56)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G56)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E56)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D56">IF(E56="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F56)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G56)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E56)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M56" t="str">
@@ -3843,7 +3864,7 @@
         <v/>
       </c>
       <c r="D57" s="23" t="str" cm="1">
-        <f t="array" ref="D57">IF(E57="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F57)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G57)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E57)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D57">IF(E57="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F57)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G57)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E57)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M57" t="str">
@@ -3861,7 +3882,7 @@
         <v/>
       </c>
       <c r="D58" s="23" t="str" cm="1">
-        <f t="array" ref="D58">IF(E58="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F58)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G58)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E58)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D58">IF(E58="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F58)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G58)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E58)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M58" t="str">
@@ -3879,7 +3900,7 @@
         <v/>
       </c>
       <c r="D59" s="23" t="str" cm="1">
-        <f t="array" ref="D59">IF(E59="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F59)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G59)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E59)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D59">IF(E59="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F59)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G59)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E59)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M59" t="str">
@@ -3897,7 +3918,7 @@
         <v/>
       </c>
       <c r="D60" s="23" t="str" cm="1">
-        <f t="array" ref="D60">IF(E60="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F60)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G60)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E60)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D60">IF(E60="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F60)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G60)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E60)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M60" t="str">
@@ -3915,7 +3936,7 @@
         <v/>
       </c>
       <c r="D61" s="23" t="str" cm="1">
-        <f t="array" ref="D61">IF(E61="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F61)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G61)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E61)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D61">IF(E61="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F61)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G61)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E61)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M61" t="str">
@@ -3933,7 +3954,7 @@
         <v/>
       </c>
       <c r="D62" s="23" t="str" cm="1">
-        <f t="array" ref="D62">IF(E62="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F62)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G62)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E62)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D62">IF(E62="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F62)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G62)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E62)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M62" t="str">
@@ -3951,7 +3972,7 @@
         <v/>
       </c>
       <c r="D63" s="23" t="str" cm="1">
-        <f t="array" ref="D63">IF(E63="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F63)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G63)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E63)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D63">IF(E63="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F63)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G63)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E63)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M63" t="str">
@@ -3969,7 +3990,7 @@
         <v/>
       </c>
       <c r="D64" s="23" t="str" cm="1">
-        <f t="array" ref="D64">IF(E64="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F64)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G64)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E64)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D64">IF(E64="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F64)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G64)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E64)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M64" t="str">
@@ -3987,7 +4008,7 @@
         <v/>
       </c>
       <c r="D65" s="23" t="str" cm="1">
-        <f t="array" ref="D65">IF(E65="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F65)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G65)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E65)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D65">IF(E65="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F65)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G65)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E65)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M65" t="str">
@@ -4005,7 +4026,7 @@
         <v/>
       </c>
       <c r="D66" s="23" t="str" cm="1">
-        <f t="array" ref="D66">IF(E66="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F66)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G66)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E66)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D66">IF(E66="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F66)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G66)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E66)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M66" t="str">
@@ -4023,7 +4044,7 @@
         <v/>
       </c>
       <c r="D67" s="23" t="str" cm="1">
-        <f t="array" ref="D67">IF(E67="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F67)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G67)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E67)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D67">IF(E67="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F67)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G67)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E67)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M67" t="str">
@@ -4041,7 +4062,7 @@
         <v/>
       </c>
       <c r="D68" s="23" t="str" cm="1">
-        <f t="array" ref="D68">IF(E68="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F68)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G68)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E68)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D68">IF(E68="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F68)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G68)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E68)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M68" t="str">
@@ -4059,7 +4080,7 @@
         <v/>
       </c>
       <c r="D69" s="23" t="str" cm="1">
-        <f t="array" ref="D69">IF(E69="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F69)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G69)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E69)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D69">IF(E69="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F69)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G69)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E69)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M69" t="str">
@@ -4077,7 +4098,7 @@
         <v/>
       </c>
       <c r="D70" s="23" t="str" cm="1">
-        <f t="array" ref="D70">IF(E70="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F70)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G70)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E70)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D70">IF(E70="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F70)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G70)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E70)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M70" t="str">
@@ -4095,7 +4116,7 @@
         <v/>
       </c>
       <c r="D71" s="23" t="str" cm="1">
-        <f t="array" ref="D71">IF(E71="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F71)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G71)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E71)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D71">IF(E71="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F71)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G71)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E71)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M71" t="str">
@@ -4113,7 +4134,7 @@
         <v/>
       </c>
       <c r="D72" s="23" t="str" cm="1">
-        <f t="array" ref="D72">IF(E72="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F72)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G72)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E72)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D72">IF(E72="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F72)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G72)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E72)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M72" t="str">
@@ -4131,7 +4152,7 @@
         <v/>
       </c>
       <c r="D73" s="23" t="str" cm="1">
-        <f t="array" ref="D73">IF(E73="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F73)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G73)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E73)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D73">IF(E73="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F73)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G73)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E73)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M73" t="str">
@@ -4149,7 +4170,7 @@
         <v/>
       </c>
       <c r="D74" s="23" t="str" cm="1">
-        <f t="array" ref="D74">IF(E74="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F74)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G74)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E74)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D74">IF(E74="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F74)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G74)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E74)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M74" t="str">
@@ -4167,7 +4188,7 @@
         <v/>
       </c>
       <c r="D75" s="23" t="str" cm="1">
-        <f t="array" ref="D75">IF(E75="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F75)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G75)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E75)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D75">IF(E75="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F75)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G75)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E75)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M75" t="str">
@@ -4185,7 +4206,7 @@
         <v/>
       </c>
       <c r="D76" s="23" t="str" cm="1">
-        <f t="array" ref="D76">IF(E76="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F76)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G76)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E76)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D76">IF(E76="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F76)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G76)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E76)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M76" t="str">
@@ -4203,7 +4224,7 @@
         <v/>
       </c>
       <c r="D77" s="23" t="str" cm="1">
-        <f t="array" ref="D77">IF(E77="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F77)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G77)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E77)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D77">IF(E77="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F77)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G77)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E77)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M77" t="str">
@@ -4221,7 +4242,7 @@
         <v/>
       </c>
       <c r="D78" s="23" t="str" cm="1">
-        <f t="array" ref="D78">IF(E78="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F78)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G78)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E78)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D78">IF(E78="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F78)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G78)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E78)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M78" t="str">
@@ -4239,7 +4260,7 @@
         <v/>
       </c>
       <c r="D79" s="23" t="str" cm="1">
-        <f t="array" ref="D79">IF(E79="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F79)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G79)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E79)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D79">IF(E79="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F79)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G79)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E79)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M79" t="str">
@@ -4257,7 +4278,7 @@
         <v/>
       </c>
       <c r="D80" s="23" t="str" cm="1">
-        <f t="array" ref="D80">IF(E80="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F80)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G80)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E80)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D80">IF(E80="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F80)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G80)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E80)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M80" t="str">
@@ -4275,7 +4296,7 @@
         <v/>
       </c>
       <c r="D81" s="23" t="str" cm="1">
-        <f t="array" ref="D81">IF(E81="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F81)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G81)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E81)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D81">IF(E81="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F81)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G81)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E81)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M81" t="str">
@@ -4293,7 +4314,7 @@
         <v/>
       </c>
       <c r="D82" s="23" t="str" cm="1">
-        <f t="array" ref="D82">IF(E82="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F82)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G82)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E82)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D82">IF(E82="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F82)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G82)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E82)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M82" t="str">
@@ -4311,7 +4332,7 @@
         <v/>
       </c>
       <c r="D83" s="23" t="str" cm="1">
-        <f t="array" ref="D83">IF(E83="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F83)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G83)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E83)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D83">IF(E83="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F83)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G83)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E83)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M83" t="str">
@@ -4329,7 +4350,7 @@
         <v/>
       </c>
       <c r="D84" s="23" t="str" cm="1">
-        <f t="array" ref="D84">IF(E84="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F84)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G84)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E84)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D84">IF(E84="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F84)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G84)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E84)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M84" t="str">
@@ -4347,7 +4368,7 @@
         <v/>
       </c>
       <c r="D85" s="23" t="str" cm="1">
-        <f t="array" ref="D85">IF(E85="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F85)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G85)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E85)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D85">IF(E85="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F85)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G85)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E85)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M85" t="str">
@@ -4365,7 +4386,7 @@
         <v/>
       </c>
       <c r="D86" s="23" t="str" cm="1">
-        <f t="array" ref="D86">IF(E86="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F86)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G86)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E86)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D86">IF(E86="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F86)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G86)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E86)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M86" t="str">
@@ -4383,7 +4404,7 @@
         <v/>
       </c>
       <c r="D87" s="23" t="str" cm="1">
-        <f t="array" ref="D87">IF(E87="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F87)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G87)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E87)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D87">IF(E87="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F87)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G87)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E87)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M87" t="str">
@@ -4401,7 +4422,7 @@
         <v/>
       </c>
       <c r="D88" s="23" t="str" cm="1">
-        <f t="array" ref="D88">IF(E88="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F88)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G88)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E88)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D88">IF(E88="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F88)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G88)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E88)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M88" t="str">
@@ -4419,7 +4440,7 @@
         <v/>
       </c>
       <c r="D89" s="23" t="str" cm="1">
-        <f t="array" ref="D89">IF(E89="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F89)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G89)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E89)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D89">IF(E89="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F89)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G89)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E89)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M89" t="str">
@@ -4437,7 +4458,7 @@
         <v/>
       </c>
       <c r="D90" s="23" t="str" cm="1">
-        <f t="array" ref="D90">IF(E90="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F90)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G90)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E90)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D90">IF(E90="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F90)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G90)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E90)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M90" t="str">
@@ -4455,7 +4476,7 @@
         <v/>
       </c>
       <c r="D91" s="23" t="str" cm="1">
-        <f t="array" ref="D91">IF(E91="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F91)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G91)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E91)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D91">IF(E91="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F91)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G91)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E91)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M91" t="str">
@@ -4473,7 +4494,7 @@
         <v/>
       </c>
       <c r="D92" s="23" t="str" cm="1">
-        <f t="array" ref="D92">IF(E92="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F92)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G92)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E92)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D92">IF(E92="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F92)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G92)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E92)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M92" t="str">
@@ -4491,7 +4512,7 @@
         <v/>
       </c>
       <c r="D93" s="23" t="str" cm="1">
-        <f t="array" ref="D93">IF(E93="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F93)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G93)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E93)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D93">IF(E93="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F93)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G93)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E93)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M93" t="str">
@@ -4509,7 +4530,7 @@
         <v/>
       </c>
       <c r="D94" s="23" t="str" cm="1">
-        <f t="array" ref="D94">IF(E94="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F94)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G94)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E94)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D94">IF(E94="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F94)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G94)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E94)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M94" t="str">
@@ -4527,7 +4548,7 @@
         <v/>
       </c>
       <c r="D95" s="23" t="str" cm="1">
-        <f t="array" ref="D95">IF(E95="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F95)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G95)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E95)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D95">IF(E95="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F95)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G95)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E95)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M95" t="str">
@@ -4545,7 +4566,7 @@
         <v/>
       </c>
       <c r="D96" s="23" t="str" cm="1">
-        <f t="array" ref="D96">IF(E96="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F96)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G96)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E96)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D96">IF(E96="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F96)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G96)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E96)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M96" t="str">
@@ -4563,7 +4584,7 @@
         <v/>
       </c>
       <c r="D97" s="23" t="str" cm="1">
-        <f t="array" ref="D97">IF(E97="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F97)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G97)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E97)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D97">IF(E97="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F97)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G97)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E97)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M97" t="str">
@@ -4581,7 +4602,7 @@
         <v/>
       </c>
       <c r="D98" s="23" t="str" cm="1">
-        <f t="array" ref="D98">IF(E98="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F98)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G98)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E98)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D98">IF(E98="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F98)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G98)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E98)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M98" t="str">
@@ -4599,7 +4620,7 @@
         <v/>
       </c>
       <c r="D99" s="23" t="str" cm="1">
-        <f t="array" ref="D99">IF(E99="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F99)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G99)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E99)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D99">IF(E99="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F99)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G99)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E99)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M99" t="str">
@@ -4617,7 +4638,7 @@
         <v/>
       </c>
       <c r="D100" s="23" t="str" cm="1">
-        <f t="array" ref="D100">IF(E100="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F100)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G100)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E100)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D100">IF(E100="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F100)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G100)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E100)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M100" t="str">
@@ -4635,7 +4656,7 @@
         <v/>
       </c>
       <c r="D101" s="23" t="str" cm="1">
-        <f t="array" ref="D101">IF(E101="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F101)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G101)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E101)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D101">IF(E101="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F101)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G101)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E101)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M101" t="str">
@@ -4653,7 +4674,7 @@
         <v/>
       </c>
       <c r="D102" s="23" t="str" cm="1">
-        <f t="array" ref="D102">IF(E102="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F102)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G102)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E102)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D102">IF(E102="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F102)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G102)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E102)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M102" t="str">
@@ -4671,7 +4692,7 @@
         <v/>
       </c>
       <c r="D103" s="23" t="str" cm="1">
-        <f t="array" ref="D103">IF(E103="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F103)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G103)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E103)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D103">IF(E103="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F103)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G103)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E103)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M103" t="str">
@@ -4689,7 +4710,7 @@
         <v/>
       </c>
       <c r="D104" s="23" t="str" cm="1">
-        <f t="array" ref="D104">IF(E104="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F104)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G104)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E104)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D104">IF(E104="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F104)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G104)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E104)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M104" t="str">
@@ -4707,7 +4728,7 @@
         <v/>
       </c>
       <c r="D105" s="23" t="str" cm="1">
-        <f t="array" ref="D105">IF(E105="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F105)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G105)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E105)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D105">IF(E105="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F105)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G105)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E105)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M105" t="str">
@@ -4725,7 +4746,7 @@
         <v/>
       </c>
       <c r="D106" s="23" t="str" cm="1">
-        <f t="array" ref="D106">IF(E106="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F106)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G106)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E106)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D106">IF(E106="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F106)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G106)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E106)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M106" t="str">
@@ -4743,7 +4764,7 @@
         <v/>
       </c>
       <c r="D107" s="23" t="str" cm="1">
-        <f t="array" ref="D107">IF(E107="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F107)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G107)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E107)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D107">IF(E107="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F107)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G107)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E107)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M107" t="str">
@@ -4761,7 +4782,7 @@
         <v/>
       </c>
       <c r="D108" s="23" t="str" cm="1">
-        <f t="array" ref="D108">IF(E108="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F108)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G108)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E108)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D108">IF(E108="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F108)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G108)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E108)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M108" t="str">
@@ -4779,7 +4800,7 @@
         <v/>
       </c>
       <c r="D109" s="23" t="str" cm="1">
-        <f t="array" ref="D109">IF(E109="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F109)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G109)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E109)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D109">IF(E109="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F109)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G109)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E109)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M109" t="str">
@@ -4797,7 +4818,7 @@
         <v/>
       </c>
       <c r="D110" s="23" t="str" cm="1">
-        <f t="array" ref="D110">IF(E110="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F110)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G110)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E110)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D110">IF(E110="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F110)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G110)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E110)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M110" t="str">
@@ -4815,7 +4836,7 @@
         <v/>
       </c>
       <c r="D111" s="23" t="str" cm="1">
-        <f t="array" ref="D111">IF(E111="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F111)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G111)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E111)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D111">IF(E111="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F111)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G111)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E111)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M111" t="str">
@@ -4833,7 +4854,7 @@
         <v/>
       </c>
       <c r="D112" s="23" t="str" cm="1">
-        <f t="array" ref="D112">IF(E112="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F112)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G112)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E112)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D112">IF(E112="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F112)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G112)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E112)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M112" t="str">
@@ -4851,7 +4872,7 @@
         <v/>
       </c>
       <c r="D113" s="23" t="str" cm="1">
-        <f t="array" ref="D113">IF(E113="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F113)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G113)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E113)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D113">IF(E113="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F113)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G113)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E113)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M113" t="str">
@@ -4869,7 +4890,7 @@
         <v/>
       </c>
       <c r="D114" s="23" t="str" cm="1">
-        <f t="array" ref="D114">IF(E114="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F114)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G114)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E114)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D114">IF(E114="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F114)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G114)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E114)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M114" t="str">
@@ -4887,7 +4908,7 @@
         <v/>
       </c>
       <c r="D115" s="23" t="str" cm="1">
-        <f t="array" ref="D115">IF(E115="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F115)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G115)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E115)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D115">IF(E115="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F115)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G115)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E115)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M115" t="str">
@@ -4905,7 +4926,7 @@
         <v/>
       </c>
       <c r="D116" s="23" t="str" cm="1">
-        <f t="array" ref="D116">IF(E116="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F116)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G116)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E116)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D116">IF(E116="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F116)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G116)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E116)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M116" t="str">
@@ -4923,7 +4944,7 @@
         <v/>
       </c>
       <c r="D117" s="23" t="str" cm="1">
-        <f t="array" ref="D117">IF(E117="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F117)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G117)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E117)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D117">IF(E117="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F117)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G117)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E117)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M117" t="str">
@@ -4941,7 +4962,7 @@
         <v/>
       </c>
       <c r="D118" s="23" t="str" cm="1">
-        <f t="array" ref="D118">IF(E118="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F118)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G118)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E118)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D118">IF(E118="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F118)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G118)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E118)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M118" t="str">
@@ -4959,7 +4980,7 @@
         <v/>
       </c>
       <c r="D119" s="23" t="str" cm="1">
-        <f t="array" ref="D119">IF(E119="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F119)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G119)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E119)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D119">IF(E119="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F119)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G119)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E119)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M119" t="str">
@@ -4977,7 +4998,7 @@
         <v/>
       </c>
       <c r="D120" s="23" t="str" cm="1">
-        <f t="array" ref="D120">IF(E120="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F120)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G120)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E120)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D120">IF(E120="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F120)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G120)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E120)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M120" t="str">
@@ -4995,7 +5016,7 @@
         <v/>
       </c>
       <c r="D121" s="23" t="str" cm="1">
-        <f t="array" ref="D121">IF(E121="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F121)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G121)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E121)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D121">IF(E121="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F121)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G121)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E121)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M121" t="str">
@@ -5013,7 +5034,7 @@
         <v/>
       </c>
       <c r="D122" s="23" t="str" cm="1">
-        <f t="array" ref="D122">IF(E122="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F122)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G122)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E122)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D122">IF(E122="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F122)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G122)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E122)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M122" t="str">
@@ -5031,7 +5052,7 @@
         <v/>
       </c>
       <c r="D123" s="23" t="str" cm="1">
-        <f t="array" ref="D123">IF(E123="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F123)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G123)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E123)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D123">IF(E123="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F123)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G123)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E123)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M123" t="str">
@@ -5049,7 +5070,7 @@
         <v/>
       </c>
       <c r="D124" s="23" t="str" cm="1">
-        <f t="array" ref="D124">IF(E124="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F124)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G124)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E124)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D124">IF(E124="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F124)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G124)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E124)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M124" t="str">
@@ -5067,7 +5088,7 @@
         <v/>
       </c>
       <c r="D125" s="23" t="str" cm="1">
-        <f t="array" ref="D125">IF(E125="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F125)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G125)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E125)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D125">IF(E125="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F125)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G125)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E125)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M125" t="str">
@@ -5085,7 +5106,7 @@
         <v/>
       </c>
       <c r="D126" s="23" t="str" cm="1">
-        <f t="array" ref="D126">IF(E126="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F126)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G126)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E126)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D126">IF(E126="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F126)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G126)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E126)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M126" t="str">
@@ -5103,7 +5124,7 @@
         <v/>
       </c>
       <c r="D127" s="23" t="str" cm="1">
-        <f t="array" ref="D127">IF(E127="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F127)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G127)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E127)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D127">IF(E127="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F127)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G127)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E127)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M127" t="str">
@@ -5121,7 +5142,7 @@
         <v/>
       </c>
       <c r="D128" s="23" t="str" cm="1">
-        <f t="array" ref="D128">IF(E128="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F128)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G128)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E128)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D128">IF(E128="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F128)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G128)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E128)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M128" t="str">
@@ -5139,7 +5160,7 @@
         <v/>
       </c>
       <c r="D129" s="23" t="str" cm="1">
-        <f t="array" ref="D129">IF(E129="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F129)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G129)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E129)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D129">IF(E129="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F129)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G129)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E129)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M129" t="str">
@@ -5157,7 +5178,7 @@
         <v/>
       </c>
       <c r="D130" s="23" t="str" cm="1">
-        <f t="array" ref="D130">IF(E130="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F130)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G130)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E130)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D130">IF(E130="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F130)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G130)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E130)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M130" t="str">
@@ -5175,7 +5196,7 @@
         <v/>
       </c>
       <c r="D131" s="23" t="str" cm="1">
-        <f t="array" ref="D131">IF(E131="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F131)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G131)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E131)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D131">IF(E131="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F131)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G131)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E131)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M131" t="str">
@@ -5193,7 +5214,7 @@
         <v/>
       </c>
       <c r="D132" s="23" t="str" cm="1">
-        <f t="array" ref="D132">IF(E132="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F132)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G132)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E132)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D132">IF(E132="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F132)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G132)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E132)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M132" t="str">
@@ -5211,7 +5232,7 @@
         <v/>
       </c>
       <c r="D133" s="23" t="str" cm="1">
-        <f t="array" ref="D133">IF(E133="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F133)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G133)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E133)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D133">IF(E133="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F133)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G133)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E133)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M133" t="str">
@@ -5229,7 +5250,7 @@
         <v/>
       </c>
       <c r="D134" s="23" t="str" cm="1">
-        <f t="array" ref="D134">IF(E134="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F134)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G134)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E134)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D134">IF(E134="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F134)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G134)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E134)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M134" t="str">
@@ -5247,7 +5268,7 @@
         <v/>
       </c>
       <c r="D135" s="23" t="str" cm="1">
-        <f t="array" ref="D135">IF(E135="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F135)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G135)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E135)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D135">IF(E135="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F135)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G135)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E135)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M135" t="str">
@@ -5265,7 +5286,7 @@
         <v/>
       </c>
       <c r="D136" s="23" t="str" cm="1">
-        <f t="array" ref="D136">IF(E136="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F136)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G136)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E136)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D136">IF(E136="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F136)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G136)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E136)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M136" t="str">
@@ -5283,7 +5304,7 @@
         <v/>
       </c>
       <c r="D137" s="23" t="str" cm="1">
-        <f t="array" ref="D137">IF(E137="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F137)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G137)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E137)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D137">IF(E137="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F137)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G137)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E137)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M137" t="str">
@@ -5301,7 +5322,7 @@
         <v/>
       </c>
       <c r="D138" s="23" t="str" cm="1">
-        <f t="array" ref="D138">IF(E138="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F138)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G138)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E138)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D138">IF(E138="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F138)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G138)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E138)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M138" t="str">
@@ -5319,7 +5340,7 @@
         <v/>
       </c>
       <c r="D139" s="23" t="str" cm="1">
-        <f t="array" ref="D139">IF(E139="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F139)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G139)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E139)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D139">IF(E139="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F139)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G139)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E139)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M139" t="str">
@@ -5337,7 +5358,7 @@
         <v/>
       </c>
       <c r="D140" s="23" t="str" cm="1">
-        <f t="array" ref="D140">IF(E140="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F140)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G140)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E140)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D140">IF(E140="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F140)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G140)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E140)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M140" t="str">
@@ -5355,7 +5376,7 @@
         <v/>
       </c>
       <c r="D141" s="23" t="str" cm="1">
-        <f t="array" ref="D141">IF(E141="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F141)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G141)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E141)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D141">IF(E141="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F141)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G141)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E141)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M141" t="str">
@@ -5373,7 +5394,7 @@
         <v/>
       </c>
       <c r="D142" s="23" t="str" cm="1">
-        <f t="array" ref="D142">IF(E142="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F142)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G142)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E142)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D142">IF(E142="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F142)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G142)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E142)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M142" t="str">
@@ -5391,7 +5412,7 @@
         <v/>
       </c>
       <c r="D143" s="23" t="str" cm="1">
-        <f t="array" ref="D143">IF(E143="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F143)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G143)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E143)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D143">IF(E143="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F143)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G143)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E143)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M143" t="str">
@@ -5409,7 +5430,7 @@
         <v/>
       </c>
       <c r="D144" s="23" t="str" cm="1">
-        <f t="array" ref="D144">IF(E144="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F144)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G144)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E144)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D144">IF(E144="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F144)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G144)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E144)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M144" t="str">
@@ -5427,7 +5448,7 @@
         <v/>
       </c>
       <c r="D145" s="23" t="str" cm="1">
-        <f t="array" ref="D145">IF(E145="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F145)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G145)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E145)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D145">IF(E145="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F145)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G145)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E145)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M145" t="str">
@@ -5445,7 +5466,7 @@
         <v/>
       </c>
       <c r="D146" s="23" t="str" cm="1">
-        <f t="array" ref="D146">IF(E146="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F146)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G146)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E146)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D146">IF(E146="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F146)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G146)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E146)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M146" t="str">
@@ -5463,7 +5484,7 @@
         <v/>
       </c>
       <c r="D147" s="23" t="str" cm="1">
-        <f t="array" ref="D147">IF(E147="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F147)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G147)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E147)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D147">IF(E147="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F147)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G147)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E147)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M147" t="str">
@@ -5481,7 +5502,7 @@
         <v/>
       </c>
       <c r="D148" s="23" t="str" cm="1">
-        <f t="array" ref="D148">IF(E148="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F148)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G148)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E148)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D148">IF(E148="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F148)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G148)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E148)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M148" t="str">
@@ -5499,7 +5520,7 @@
         <v/>
       </c>
       <c r="D149" s="23" t="str" cm="1">
-        <f t="array" ref="D149">IF(E149="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F149)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G149)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E149)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D149">IF(E149="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F149)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G149)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E149)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M149" t="str">
@@ -5517,7 +5538,7 @@
         <v/>
       </c>
       <c r="D150" s="23" t="str" cm="1">
-        <f t="array" ref="D150">IF(E150="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F150)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G150)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E150)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D150">IF(E150="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F150)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G150)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E150)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M150" t="str">
@@ -5535,7 +5556,7 @@
         <v/>
       </c>
       <c r="D151" s="23" t="str" cm="1">
-        <f t="array" ref="D151">IF(E151="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F151)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G151)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E151)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D151">IF(E151="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F151)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G151)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E151)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M151" t="str">
@@ -5553,7 +5574,7 @@
         <v/>
       </c>
       <c r="D152" s="23" t="str" cm="1">
-        <f t="array" ref="D152">IF(E152="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F152)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G152)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E152)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D152">IF(E152="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F152)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G152)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E152)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M152" t="str">
@@ -5571,7 +5592,7 @@
         <v/>
       </c>
       <c r="D153" s="23" t="str" cm="1">
-        <f t="array" ref="D153">IF(E153="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F153)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G153)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E153)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D153">IF(E153="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F153)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G153)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E153)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M153" t="str">
@@ -5589,7 +5610,7 @@
         <v/>
       </c>
       <c r="D154" s="23" t="str" cm="1">
-        <f t="array" ref="D154">IF(E154="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F154)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G154)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E154)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D154">IF(E154="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F154)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G154)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E154)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M154" t="str">
@@ -5607,7 +5628,7 @@
         <v/>
       </c>
       <c r="D155" s="23" t="str" cm="1">
-        <f t="array" ref="D155">IF(E155="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F155)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G155)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E155)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D155">IF(E155="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F155)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G155)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E155)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M155" t="str">
@@ -5625,7 +5646,7 @@
         <v/>
       </c>
       <c r="D156" s="23" t="str" cm="1">
-        <f t="array" ref="D156">IF(E156="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F156)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G156)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E156)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D156">IF(E156="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F156)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G156)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E156)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M156" t="str">
@@ -5643,7 +5664,7 @@
         <v/>
       </c>
       <c r="D157" s="23" t="str" cm="1">
-        <f t="array" ref="D157">IF(E157="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F157)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G157)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E157)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D157">IF(E157="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F157)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G157)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E157)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M157" t="str">
@@ -5661,7 +5682,7 @@
         <v/>
       </c>
       <c r="D158" s="23" t="str" cm="1">
-        <f t="array" ref="D158">IF(E158="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F158)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G158)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E158)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D158">IF(E158="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F158)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G158)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E158)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M158" t="str">
@@ -5679,7 +5700,7 @@
         <v/>
       </c>
       <c r="D159" s="23" t="str" cm="1">
-        <f t="array" ref="D159">IF(E159="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F159)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G159)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E159)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D159">IF(E159="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F159)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G159)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E159)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M159" t="str">
@@ -5697,7 +5718,7 @@
         <v/>
       </c>
       <c r="D160" s="23" t="str" cm="1">
-        <f t="array" ref="D160">IF(E160="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F160)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G160)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E160)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D160">IF(E160="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F160)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G160)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E160)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M160" t="str">
@@ -5715,7 +5736,7 @@
         <v/>
       </c>
       <c r="D161" s="23" t="str" cm="1">
-        <f t="array" ref="D161">IF(E161="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F161)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G161)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E161)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D161">IF(E161="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F161)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G161)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E161)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M161" t="str">
@@ -5733,7 +5754,7 @@
         <v/>
       </c>
       <c r="D162" s="23" t="str" cm="1">
-        <f t="array" ref="D162">IF(E162="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F162)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G162)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E162)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D162">IF(E162="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F162)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G162)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E162)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M162" t="str">
@@ -5751,7 +5772,7 @@
         <v/>
       </c>
       <c r="D163" s="23" t="str" cm="1">
-        <f t="array" ref="D163">IF(E163="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F163)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G163)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E163)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D163">IF(E163="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F163)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G163)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E163)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M163" t="str">
@@ -5769,7 +5790,7 @@
         <v/>
       </c>
       <c r="D164" s="23" t="str" cm="1">
-        <f t="array" ref="D164">IF(E164="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F164)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G164)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E164)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D164">IF(E164="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F164)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G164)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E164)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M164" t="str">
@@ -5787,7 +5808,7 @@
         <v/>
       </c>
       <c r="D165" s="23" t="str" cm="1">
-        <f t="array" ref="D165">IF(E165="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F165)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G165)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E165)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D165">IF(E165="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F165)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G165)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E165)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M165" t="str">
@@ -5805,7 +5826,7 @@
         <v/>
       </c>
       <c r="D166" s="23" t="str" cm="1">
-        <f t="array" ref="D166">IF(E166="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F166)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G166)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E166)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D166">IF(E166="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F166)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G166)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E166)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M166" t="str">
@@ -5823,7 +5844,7 @@
         <v/>
       </c>
       <c r="D167" s="23" t="str" cm="1">
-        <f t="array" ref="D167">IF(E167="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F167)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G167)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E167)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D167">IF(E167="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F167)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G167)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E167)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M167" t="str">
@@ -5841,7 +5862,7 @@
         <v/>
       </c>
       <c r="D168" s="23" t="str" cm="1">
-        <f t="array" ref="D168">IF(E168="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F168)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G168)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E168)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D168">IF(E168="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F168)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G168)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E168)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M168" t="str">
@@ -5859,7 +5880,7 @@
         <v/>
       </c>
       <c r="D169" s="23" t="str" cm="1">
-        <f t="array" ref="D169">IF(E169="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F169)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G169)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E169)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D169">IF(E169="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F169)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G169)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E169)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M169" t="str">
@@ -5877,7 +5898,7 @@
         <v/>
       </c>
       <c r="D170" s="23" t="str" cm="1">
-        <f t="array" ref="D170">IF(E170="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F170)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G170)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E170)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D170">IF(E170="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F170)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G170)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E170)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M170" t="str">
@@ -5895,7 +5916,7 @@
         <v/>
       </c>
       <c r="D171" s="23" t="str" cm="1">
-        <f t="array" ref="D171">IF(E171="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F171)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G171)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E171)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D171">IF(E171="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F171)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G171)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E171)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M171" t="str">
@@ -5913,7 +5934,7 @@
         <v/>
       </c>
       <c r="D172" s="23" t="str" cm="1">
-        <f t="array" ref="D172">IF(E172="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F172)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G172)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E172)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D172">IF(E172="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F172)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G172)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E172)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M172" t="str">
@@ -5931,7 +5952,7 @@
         <v/>
       </c>
       <c r="D173" s="23" t="str" cm="1">
-        <f t="array" ref="D173">IF(E173="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F173)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G173)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E173)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D173">IF(E173="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F173)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G173)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E173)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M173" t="str">
@@ -5949,7 +5970,7 @@
         <v/>
       </c>
       <c r="D174" s="23" t="str" cm="1">
-        <f t="array" ref="D174">IF(E174="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F174)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G174)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E174)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D174">IF(E174="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F174)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G174)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E174)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M174" t="str">
@@ -5967,7 +5988,7 @@
         <v/>
       </c>
       <c r="D175" s="23" t="str" cm="1">
-        <f t="array" ref="D175">IF(E175="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F175)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G175)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E175)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D175">IF(E175="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F175)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G175)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E175)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M175" t="str">
@@ -5985,7 +6006,7 @@
         <v/>
       </c>
       <c r="D176" s="23" t="str" cm="1">
-        <f t="array" ref="D176">IF(E176="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F176)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G176)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E176)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D176">IF(E176="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F176)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G176)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E176)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M176" t="str">
@@ -6003,7 +6024,7 @@
         <v/>
       </c>
       <c r="D177" s="23" t="str" cm="1">
-        <f t="array" ref="D177">IF(E177="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F177)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G177)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E177)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D177">IF(E177="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F177)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G177)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E177)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M177" t="str">
@@ -6021,7 +6042,7 @@
         <v/>
       </c>
       <c r="D178" s="23" t="str" cm="1">
-        <f t="array" ref="D178">IF(E178="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F178)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G178)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E178)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D178">IF(E178="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F178)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G178)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E178)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M178" t="str">
@@ -6039,7 +6060,7 @@
         <v/>
       </c>
       <c r="D179" s="23" t="str" cm="1">
-        <f t="array" ref="D179">IF(E179="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F179)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G179)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E179)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D179">IF(E179="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F179)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G179)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E179)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M179" t="str">
@@ -6057,7 +6078,7 @@
         <v/>
       </c>
       <c r="D180" s="23" t="str" cm="1">
-        <f t="array" ref="D180">IF(E180="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F180)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G180)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E180)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D180">IF(E180="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F180)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G180)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E180)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M180" t="str">
@@ -6075,7 +6096,7 @@
         <v/>
       </c>
       <c r="D181" s="23" t="str" cm="1">
-        <f t="array" ref="D181">IF(E181="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F181)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G181)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E181)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D181">IF(E181="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F181)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G181)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E181)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M181" t="str">
@@ -6093,7 +6114,7 @@
         <v/>
       </c>
       <c r="D182" s="23" t="str" cm="1">
-        <f t="array" ref="D182">IF(E182="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F182)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G182)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E182)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D182">IF(E182="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F182)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G182)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E182)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M182" t="str">
@@ -6111,7 +6132,7 @@
         <v/>
       </c>
       <c r="D183" s="23" t="str" cm="1">
-        <f t="array" ref="D183">IF(E183="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F183)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G183)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E183)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D183">IF(E183="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F183)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G183)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E183)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M183" t="str">
@@ -6129,7 +6150,7 @@
         <v/>
       </c>
       <c r="D184" s="23" t="str" cm="1">
-        <f t="array" ref="D184">IF(E184="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F184)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G184)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E184)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D184">IF(E184="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F184)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G184)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E184)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M184" t="str">
@@ -6147,7 +6168,7 @@
         <v/>
       </c>
       <c r="D185" s="23" t="str" cm="1">
-        <f t="array" ref="D185">IF(E185="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F185)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G185)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E185)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D185">IF(E185="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F185)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G185)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E185)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M185" t="str">
@@ -6165,7 +6186,7 @@
         <v/>
       </c>
       <c r="D186" s="23" t="str" cm="1">
-        <f t="array" ref="D186">IF(E186="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F186)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G186)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E186)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D186">IF(E186="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F186)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G186)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E186)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M186" t="str">
@@ -6183,7 +6204,7 @@
         <v/>
       </c>
       <c r="D187" s="23" t="str" cm="1">
-        <f t="array" ref="D187">IF(E187="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F187)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G187)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E187)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D187">IF(E187="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F187)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G187)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E187)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M187" t="str">
@@ -6201,7 +6222,7 @@
         <v/>
       </c>
       <c r="D188" s="23" t="str" cm="1">
-        <f t="array" ref="D188">IF(E188="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F188)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G188)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E188)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D188">IF(E188="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F188)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G188)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E188)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M188" t="str">
@@ -6219,7 +6240,7 @@
         <v/>
       </c>
       <c r="D189" s="23" t="str" cm="1">
-        <f t="array" ref="D189">IF(E189="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F189)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G189)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E189)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D189">IF(E189="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F189)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G189)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E189)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M189" t="str">
@@ -6237,7 +6258,7 @@
         <v/>
       </c>
       <c r="D190" s="23" t="str" cm="1">
-        <f t="array" ref="D190">IF(E190="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F190)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G190)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E190)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D190">IF(E190="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F190)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G190)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E190)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M190" t="str">
@@ -6255,7 +6276,7 @@
         <v/>
       </c>
       <c r="D191" s="23" t="str" cm="1">
-        <f t="array" ref="D191">IF(E191="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F191)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G191)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E191)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D191">IF(E191="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F191)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G191)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E191)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M191" t="str">
@@ -6273,7 +6294,7 @@
         <v/>
       </c>
       <c r="D192" s="23" t="str" cm="1">
-        <f t="array" ref="D192">IF(E192="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F192)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G192)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E192)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D192">IF(E192="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F192)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G192)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E192)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M192" t="str">
@@ -6291,7 +6312,7 @@
         <v/>
       </c>
       <c r="D193" s="23" t="str" cm="1">
-        <f t="array" ref="D193">IF(E193="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F193)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G193)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E193)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D193">IF(E193="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F193)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G193)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E193)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M193" t="str">
@@ -6309,7 +6330,7 @@
         <v/>
       </c>
       <c r="D194" s="23" t="str" cm="1">
-        <f t="array" ref="D194">IF(E194="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F194)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G194)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E194)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D194">IF(E194="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F194)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G194)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E194)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M194" t="str">
@@ -6327,7 +6348,7 @@
         <v/>
       </c>
       <c r="D195" s="23" t="str" cm="1">
-        <f t="array" ref="D195">IF(E195="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F195)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G195)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E195)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D195">IF(E195="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F195)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G195)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E195)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M195" t="str">
@@ -6345,7 +6366,7 @@
         <v/>
       </c>
       <c r="D196" s="23" t="str" cm="1">
-        <f t="array" ref="D196">IF(E196="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F196)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G196)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E196)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D196">IF(E196="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F196)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G196)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E196)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M196" t="str">
@@ -6363,7 +6384,7 @@
         <v/>
       </c>
       <c r="D197" s="23" t="str" cm="1">
-        <f t="array" ref="D197">IF(E197="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F197)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G197)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E197)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D197">IF(E197="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F197)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G197)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E197)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M197" t="str">
@@ -6381,7 +6402,7 @@
         <v/>
       </c>
       <c r="D198" s="23" t="str" cm="1">
-        <f t="array" ref="D198">IF(E198="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F198)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G198)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E198)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D198">IF(E198="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F198)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G198)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E198)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M198" t="str">
@@ -6399,7 +6420,7 @@
         <v/>
       </c>
       <c r="D199" s="23" t="str" cm="1">
-        <f t="array" ref="D199">IF(E199="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F199)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G199)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E199)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D199">IF(E199="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F199)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G199)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E199)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M199" t="str">
@@ -6417,7 +6438,7 @@
         <v/>
       </c>
       <c r="D200" s="23" t="str" cm="1">
-        <f t="array" ref="D200">IF(E200="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F200)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G200)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$W$4:$W$33,_xlpm.abr,NPF!$X$4:$X$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E200)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
+        <f t="array" ref="D200">IF(E200="","",_xlfn.LET(_xlpm.cat,_xlfn.XLOOKUP(UPPER(TRIM(F200)),UPPER(NPF!$G$4:$G$40),NPF!$H$4:$H$40,"¿CAT?"),_xlpm.comb,_xlfn.XLOOKUP(UPPER(TRIM(G200)),UPPER(NPF!$A$4:$A$30),NPF!$B$4:$B$30,"¿COMB?"),_xlpm.txt,NPF!$V$4:$V$33,_xlpm.abr,NPF!$W$4:$W$33,_xlpm.modAbrev,_xlfn.REDUCE(UPPER(TRIM(E200)),_xlfn.SEQUENCE(ROWS(_xlpm.txt)),_xlfn.LAMBDA(_xlpm.acc,_xlpm.i,IF(INDEX(_xlpm.txt,_xlpm.i)="",_xlpm.acc,SUBSTITUTE(_xlpm.acc,UPPER(INDEX(_xlpm.txt,_xlpm.i)),INDEX(_xlpm.abr,_xlpm.i))))),_xlpm.modelo,SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlpm.modAbrev," ",""),"(",""),")",""),_xlpm.cat&amp;"-"&amp;_xlpm.modelo&amp;"-"&amp;_xlpm.comb))</f>
         <v/>
       </c>
       <c r="M200" t="str">
@@ -6526,7 +6547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG40"/>
+  <dimension ref="A1:AF40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -6548,51 +6569,50 @@
     <col min="18" max="18" width="3" customWidth="1"/>
     <col min="19" max="19" width="28" customWidth="1"/>
     <col min="20" max="20" width="3" customWidth="1"/>
-    <col min="21" max="21" width="12" customWidth="1"/>
-    <col min="22" max="22" width="8.7109375" customWidth="1"/>
-    <col min="23" max="23" width="22" customWidth="1"/>
-    <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="40" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
-    <col min="27" max="27" width="24" customWidth="1"/>
-    <col min="28" max="28" width="48" customWidth="1"/>
-    <col min="29" max="29" width="34" customWidth="1"/>
-    <col min="30" max="30" width="40" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" customWidth="1"/>
-    <col min="32" max="32" width="43" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.7109375" customWidth="1"/>
+    <col min="21" max="21" width="8.7109375" customWidth="1"/>
+    <col min="22" max="22" width="22" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="40" customWidth="1"/>
+    <col min="25" max="25" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="24" customWidth="1"/>
+    <col min="27" max="27" width="48" customWidth="1"/>
+    <col min="28" max="28" width="34" customWidth="1"/>
+    <col min="29" max="29" width="40" customWidth="1"/>
+    <col min="30" max="30" width="8.7109375" customWidth="1"/>
+    <col min="31" max="31" width="43" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="24" t="s">
+      <c r="V1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="AA1" s="25" t="s">
+      <c r="Z1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="AF1" s="24" t="s">
+      <c r="AE1" s="24" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="W2" s="38" t="s">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="V2" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="AA2" s="26" t="s">
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Z2" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="AF2" s="38" t="s">
+      <c r="AE2" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="AG2" s="39"/>
-    </row>
-    <row r="3" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF2" s="41"/>
+    </row>
+    <row r="3" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>19</v>
       </c>
@@ -6627,7 +6647,7 @@
       <c r="S3" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="U3" s="27" t="s">
+      <c r="V3" s="27" t="s">
         <v>28</v>
       </c>
       <c r="W3" s="27" t="s">
@@ -6636,909 +6656,908 @@
       <c r="X3" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="Y3" s="27" t="s">
+      <c r="AE3" s="27" t="s">
         <v>31</v>
       </c>
       <c r="AF3" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="AG3" s="27" t="s">
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="B4" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="D4" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="E4" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="G4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="H4" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="L4" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="N4" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="30" t="s">
+      <c r="O4" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="Q4" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="Q4" s="29" t="s">
+      <c r="S4" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="29" t="s">
+      <c r="W4" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="U4" s="29">
-        <v>1</v>
-      </c>
-      <c r="W4" s="31" t="s">
+      <c r="X4" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="X4" s="31" t="s">
+      <c r="Z4" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="Y4" s="29" t="s">
+      <c r="AE4" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="AA4" s="32" t="s">
+      <c r="AF4" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="AF4" s="31" t="s">
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A5" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="AG4" s="31" t="s">
+      <c r="B5" s="29" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="D5" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="E5" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="G5" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="H5" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="J5" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="L5" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="N5" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="Q5" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="S5" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="V5" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="W5" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="X5" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z5" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB5" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="AC5" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE5" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF5" s="31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="S5" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="U5" s="29">
-        <v>2</v>
-      </c>
-      <c r="W5" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="X5" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y5" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA5" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB5" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC5" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD5" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF5" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="AG5" s="31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="33" t="s">
+      <c r="N6" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="S6" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="H6" s="29" t="s">
+      <c r="V6" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="W6" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="L6" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="O6" s="30" t="s">
+      <c r="X6" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="S6" s="29" t="s">
+      <c r="Z6" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="W6" s="31" t="s">
+      <c r="AA6" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="X6" s="31" t="s">
+      <c r="AB6" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="Y6" s="29" t="s">
+      <c r="AC6" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="AA6" s="34" t="s">
+      <c r="AE6" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="AB6" s="34" t="s">
+      <c r="AF6" s="31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="AC6" s="34" t="s">
+      <c r="B7" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="AD6" s="35" t="s">
+      <c r="D7" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="AF6" s="31" t="s">
+      <c r="E7" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="AG6" s="31" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="G7" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="H7" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="J7" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="L7" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="N7" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="O7" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="S7" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="V7" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="W7" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="X7" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="N7" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="O7" s="30" t="s">
+      <c r="Z7" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="S7" s="29" t="s">
+      <c r="AA7" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="W7" s="31" t="s">
+      <c r="AB7" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="X7" s="31" t="s">
+      <c r="AC7" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="Y7" s="29" t="s">
+      <c r="AE7" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="AA7" s="34" t="s">
+      <c r="AF7" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AB7" s="34" t="s">
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="AC7" s="34" t="s">
+      <c r="B8" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="AD7" s="34" t="s">
+      <c r="G8" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="AF7" s="31" t="s">
+      <c r="H8" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" s="29" t="s">
         <v>104</v>
-      </c>
-      <c r="AG7" s="31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>109</v>
       </c>
       <c r="N8" s="29"/>
       <c r="O8" s="36"/>
       <c r="S8" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="V8" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="W8" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="X8" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z8" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA8" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB8" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="W8" s="31" t="s">
+      <c r="AC8" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="X8" s="31" t="s">
+      <c r="AE8" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="Y8" s="29" t="s">
+      <c r="AF8" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="AA8" s="35" t="s">
+    </row>
+    <row r="9" spans="1:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="AB8" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="AC8" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="AD8" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF8" s="31" t="s">
+      <c r="B9" s="29" t="s">
+        <v>653</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="H9" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="J9" s="29" t="s">
         <v>118</v>
-      </c>
-      <c r="AG8" s="31" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>662</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>124</v>
       </c>
       <c r="N9" s="29"/>
       <c r="O9" s="36"/>
       <c r="S9" s="29" t="s">
-        <v>44</v>
+        <v>87</v>
+      </c>
+      <c r="V9" s="31" t="s">
+        <v>119</v>
       </c>
       <c r="W9" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="X9" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z9" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA9" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB9" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC9" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="X9" s="31" t="s">
+      <c r="AE9" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="Y9" s="29" t="s">
+      <c r="AF9" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="AA9" s="34" t="s">
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="AB9" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="AC9" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="AD9" s="34" t="s">
+      <c r="B10" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="J10" s="29" t="s">
         <v>131</v>
-      </c>
-      <c r="AF9" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG9" s="31" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>137</v>
       </c>
       <c r="N10" s="29"/>
       <c r="O10" s="36"/>
       <c r="S10" s="29" t="s">
-        <v>61</v>
+        <v>103</v>
+      </c>
+      <c r="V10" s="31" t="s">
+        <v>132</v>
       </c>
       <c r="W10" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="X10" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z10" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA10" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB10" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC10" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="X10" s="31" t="s">
+      <c r="AE10" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="Y10" s="29" t="s">
+      <c r="AF10" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="AA10" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="AB10" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="AC10" s="34" t="s">
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="G11" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="S11" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="V11" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="AD10" s="34" t="s">
+      <c r="W11" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="AF10" s="31" t="s">
+      <c r="X11" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z11" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="AG10" s="31" t="s">
+      <c r="AA11" s="34" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G11" s="29" t="s">
+      <c r="AB11" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="AC11" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="S11" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="W11" s="31" t="s">
+      <c r="AE11" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="X11" s="31" t="s">
+      <c r="AF11" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="Y11" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA11" s="34" t="s">
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="G12" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="S12" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="V12" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="W12" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="X12" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="Z12" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA12" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB12" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC12" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="AE12" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="AF12" s="31" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="G13" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="S13" s="29" t="s">
+        <v>663</v>
+      </c>
+      <c r="V13" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="W13" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="X13" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z13" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA13" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB13" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="AC13" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE13" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF13" s="31" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="G14" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="S14" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="AB11" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC11" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="AD11" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="AF11" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="AG11" s="31" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G12" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="S12" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="W12" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="X12" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y12" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA12" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="AB12" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="AC12" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="AD12" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="AF12" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="AG12" s="31" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G13" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="S13" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="W13" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="X13" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y13" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA13" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="AB13" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC13" s="34" t="s">
+      <c r="V14" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="AD13" s="34" t="s">
+      <c r="W14" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="AF13" s="31" t="s">
+      <c r="X14" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="AG13" s="31" t="s">
+      <c r="AE14" s="31" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G14" s="29" t="s">
+      <c r="AF14" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="H14" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="S14" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="W14" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="X14" s="31" t="s">
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="G15" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="S15" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="V15" s="31"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="29"/>
+      <c r="Z15" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="Y14" s="29" t="s">
+      <c r="AE15" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="AF14" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="AG14" s="31" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G15" s="29" t="s">
+      <c r="AF15" s="31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="G16" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>196</v>
+      </c>
+      <c r="S16" s="29" t="s">
+        <v>659</v>
+      </c>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="29"/>
+      <c r="Z16" s="40" t="s">
         <v>186</v>
       </c>
-      <c r="H15" s="29" t="s">
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="41"/>
+      <c r="AC16" s="41"/>
+      <c r="AE16" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="S15" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="W15" s="31"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="29"/>
-      <c r="AA15" s="32" t="s">
+      <c r="AF16" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="AF15" s="31" t="s">
+    </row>
+    <row r="17" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G17" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="S17" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="AG15" s="31" t="s">
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="29"/>
+      <c r="Z17" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="41"/>
+      <c r="AC17" s="41"/>
+      <c r="AE17" s="31"/>
+      <c r="AF17" s="31"/>
+    </row>
+    <row r="18" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G18" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="H18" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="S18" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="29"/>
+      <c r="Z18" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA18" s="41"/>
+      <c r="AB18" s="41"/>
+      <c r="AC18" s="41"/>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="31"/>
+    </row>
+    <row r="19" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G19" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="H19" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="S19" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="29"/>
+      <c r="AE19" s="31"/>
+      <c r="AF19" s="31"/>
+    </row>
+    <row r="20" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G20" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="H20" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="S20" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="29"/>
+      <c r="Z20" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="31"/>
+    </row>
+    <row r="21" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G21" s="36" t="s">
+        <v>657</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>658</v>
+      </c>
+      <c r="S21" s="29" t="s">
+        <v>657</v>
+      </c>
+      <c r="V21" s="31"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="29"/>
+      <c r="Z21" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA21" s="41"/>
+      <c r="AB21" s="41"/>
+      <c r="AC21" s="41"/>
+      <c r="AE21" s="31"/>
+      <c r="AF21" s="31"/>
+    </row>
+    <row r="22" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G22" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="S22" s="29" t="s">
+        <v>661</v>
+      </c>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="29"/>
+      <c r="Z22" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="41"/>
+      <c r="AC22" s="41"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+    </row>
+    <row r="23" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G23" s="36" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="G16" s="29" t="s">
+      <c r="H23" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="H16" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="S16" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="29"/>
-      <c r="AA16" s="40" t="s">
+      <c r="S23" s="29"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="29"/>
+      <c r="Z23" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA23" s="41"/>
+      <c r="AB23" s="41"/>
+      <c r="AC23" s="41"/>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="31"/>
+    </row>
+    <row r="24" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G24" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="AB16" s="39"/>
-      <c r="AC16" s="39"/>
-      <c r="AD16" s="39"/>
-      <c r="AF16" s="31" t="s">
+      <c r="H24" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="AG16" s="31" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="17" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G17" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="S17" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="W17" s="31"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="29"/>
-      <c r="AA17" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="AB17" s="39"/>
-      <c r="AC17" s="39"/>
-      <c r="AD17" s="39"/>
-      <c r="AF17" s="31"/>
-      <c r="AG17" s="31"/>
-    </row>
-    <row r="18" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G18" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="S18" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="W18" s="31"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="29"/>
-      <c r="AA18" s="41" t="s">
-        <v>200</v>
-      </c>
-      <c r="AB18" s="39"/>
-      <c r="AC18" s="39"/>
-      <c r="AD18" s="39"/>
-      <c r="AF18" s="31"/>
-      <c r="AG18" s="31"/>
-    </row>
-    <row r="19" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G19" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="S19" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="W19" s="31"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="29"/>
-      <c r="AF19" s="31"/>
-      <c r="AG19" s="31"/>
-    </row>
-    <row r="20" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G20" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="S20" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="29"/>
-      <c r="AA20" s="32" t="s">
-        <v>205</v>
-      </c>
-      <c r="AF20" s="31"/>
-      <c r="AG20" s="31"/>
-    </row>
-    <row r="21" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G21" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="S21" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="W21" s="31"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="29"/>
-      <c r="AA21" s="40" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB21" s="39"/>
-      <c r="AC21" s="39"/>
-      <c r="AD21" s="39"/>
-      <c r="AF21" s="31"/>
-      <c r="AG21" s="31"/>
-    </row>
-    <row r="22" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G22" s="29" t="s">
+      <c r="S24" s="29"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="29"/>
+      <c r="Z24" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="H22" s="29" t="s">
+      <c r="AA24" s="41"/>
+      <c r="AB24" s="41"/>
+      <c r="AC24" s="41"/>
+      <c r="AE24" s="31"/>
+      <c r="AF24" s="31"/>
+    </row>
+    <row r="25" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G25" s="36" t="s">
+        <v>659</v>
+      </c>
+      <c r="H25" s="36" t="s">
+        <v>660</v>
+      </c>
+      <c r="S25" s="29"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="29"/>
+      <c r="Z25" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="S22" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="W22" s="31"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="29"/>
-      <c r="AA22" s="40" t="s">
+      <c r="AA25" s="41"/>
+      <c r="AB25" s="41"/>
+      <c r="AC25" s="41"/>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="31"/>
+    </row>
+    <row r="26" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G26" s="36" t="s">
+        <v>661</v>
+      </c>
+      <c r="H26" s="36" t="s">
+        <v>662</v>
+      </c>
+      <c r="S26" s="29"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="29"/>
+      <c r="Z26" s="40" t="s">
         <v>211</v>
       </c>
-      <c r="AB22" s="39"/>
-      <c r="AC22" s="39"/>
-      <c r="AD22" s="39"/>
-      <c r="AF22" s="31"/>
-      <c r="AG22" s="31"/>
-    </row>
-    <row r="23" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="G23" s="29" t="s">
+      <c r="AA26" s="41"/>
+      <c r="AB26" s="41"/>
+      <c r="AC26" s="41"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
+    </row>
+    <row r="27" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="G27" s="36" t="s">
+        <v>663</v>
+      </c>
+      <c r="H27" s="36" t="s">
+        <v>664</v>
+      </c>
+      <c r="S27" s="29"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="29"/>
+      <c r="Z27" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="H23" s="29" t="s">
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="41"/>
+      <c r="AE27" s="31"/>
+      <c r="AF27" s="31"/>
+    </row>
+    <row r="28" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S28" s="29"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="29"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+    </row>
+    <row r="29" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S29" s="29"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="29"/>
+      <c r="Z29" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="S23" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="29"/>
-      <c r="AA23" s="40" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB23" s="39"/>
-      <c r="AC23" s="39"/>
-      <c r="AD23" s="39"/>
-      <c r="AF23" s="31"/>
-      <c r="AG23" s="31"/>
-    </row>
-    <row r="24" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S24" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="29"/>
-      <c r="AA24" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB24" s="39"/>
-      <c r="AC24" s="39"/>
-      <c r="AD24" s="39"/>
-      <c r="AF24" s="31"/>
-      <c r="AG24" s="31"/>
-    </row>
-    <row r="25" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S25" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="W25" s="31"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="29"/>
-      <c r="AA25" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB25" s="39"/>
-      <c r="AC25" s="39"/>
-      <c r="AD25" s="39"/>
-      <c r="AF25" s="31"/>
-      <c r="AG25" s="31"/>
-    </row>
-    <row r="26" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S26" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="29"/>
-      <c r="AA26" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="AB26" s="39"/>
-      <c r="AC26" s="39"/>
-      <c r="AD26" s="39"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-    </row>
-    <row r="27" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S27" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="29"/>
-      <c r="AA27" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="AB27" s="39"/>
-      <c r="AC27" s="39"/>
-      <c r="AD27" s="39"/>
-      <c r="AF27" s="31"/>
-      <c r="AG27" s="31"/>
-    </row>
-    <row r="28" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S28" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="29"/>
-      <c r="AF28" s="31"/>
-      <c r="AG28" s="31"/>
-    </row>
-    <row r="29" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S29" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="W29" s="31"/>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="29"/>
-      <c r="AA29" s="37" t="s">
-        <v>219</v>
-      </c>
+      <c r="AE29" s="31"/>
       <c r="AF29" s="31"/>
-      <c r="AG29" s="31"/>
-    </row>
-    <row r="30" spans="7:33" x14ac:dyDescent="0.25">
-      <c r="S30" s="29" t="s">
-        <v>212</v>
-      </c>
+    </row>
+    <row r="30" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="S30" s="29"/>
+      <c r="V30" s="31"/>
       <c r="W30" s="31"/>
-      <c r="X30" s="31"/>
-      <c r="Y30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="AE30" s="31"/>
       <c r="AF30" s="31"/>
-      <c r="AG30" s="31"/>
-    </row>
-    <row r="31" spans="7:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="V31" s="31"/>
       <c r="W31" s="31"/>
-      <c r="X31" s="31"/>
-      <c r="Y31" s="29"/>
+      <c r="X31" s="29"/>
+      <c r="AE31" s="31"/>
       <c r="AF31" s="31"/>
-      <c r="AG31" s="31"/>
-    </row>
-    <row r="32" spans="7:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="7:32" x14ac:dyDescent="0.25">
+      <c r="V32" s="31"/>
       <c r="W32" s="31"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="29"/>
+      <c r="X32" s="29"/>
+      <c r="AE32" s="31"/>
       <c r="AF32" s="31"/>
-      <c r="AG32" s="31"/>
-    </row>
-    <row r="33" spans="23:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="22:32" x14ac:dyDescent="0.25">
+      <c r="V33" s="31"/>
       <c r="W33" s="31"/>
-      <c r="X33" s="31"/>
-      <c r="Y33" s="29"/>
+      <c r="X33" s="29"/>
+      <c r="AE33" s="31"/>
       <c r="AF33" s="31"/>
-      <c r="AG33" s="31"/>
-    </row>
-    <row r="34" spans="23:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="22:32" x14ac:dyDescent="0.25">
+      <c r="AE34" s="31"/>
       <c r="AF34" s="31"/>
-      <c r="AG34" s="31"/>
-    </row>
-    <row r="35" spans="23:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="22:32" x14ac:dyDescent="0.25">
+      <c r="AE35" s="31"/>
       <c r="AF35" s="31"/>
-      <c r="AG35" s="31"/>
-    </row>
-    <row r="36" spans="23:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="22:32" x14ac:dyDescent="0.25">
+      <c r="AE36" s="31"/>
       <c r="AF36" s="31"/>
-      <c r="AG36" s="31"/>
-    </row>
-    <row r="37" spans="23:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="22:32" x14ac:dyDescent="0.25">
+      <c r="AE37" s="31"/>
       <c r="AF37" s="31"/>
-      <c r="AG37" s="31"/>
-    </row>
-    <row r="38" spans="23:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="22:32" x14ac:dyDescent="0.25">
+      <c r="AE38" s="31"/>
       <c r="AF38" s="31"/>
-      <c r="AG38" s="31"/>
-    </row>
-    <row r="39" spans="23:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="22:32" x14ac:dyDescent="0.25">
+      <c r="AE39" s="31"/>
       <c r="AF39" s="31"/>
-      <c r="AG39" s="31"/>
-    </row>
-    <row r="40" spans="23:33" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="22:32" x14ac:dyDescent="0.25">
+      <c r="AE40" s="31"/>
       <c r="AF40" s="31"/>
-      <c r="AG40" s="31"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <mergeCells count="12">
-    <mergeCell ref="AA27:AD27"/>
-    <mergeCell ref="AA22:AD22"/>
-    <mergeCell ref="AA26:AD26"/>
-    <mergeCell ref="AA17:AD17"/>
-    <mergeCell ref="AA18:AD18"/>
-    <mergeCell ref="AA21:AD21"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="AA24:AD24"/>
-    <mergeCell ref="AA16:AD16"/>
-    <mergeCell ref="AA25:AD25"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="AA23:AD23"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="Z24:AC24"/>
+    <mergeCell ref="Z16:AC16"/>
+    <mergeCell ref="Z25:AC25"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="Z23:AC23"/>
+    <mergeCell ref="Z27:AC27"/>
+    <mergeCell ref="Z22:AC22"/>
+    <mergeCell ref="Z26:AC26"/>
+    <mergeCell ref="Z17:AC17"/>
+    <mergeCell ref="Z18:AC18"/>
+    <mergeCell ref="Z21:AC21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7558,1902 +7577,1902 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D3" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>236</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>618</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C5" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F5" s="21" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B9" s="21">
         <v>3</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E13" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C13" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F13" s="21" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F19" s="21" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C20" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="F20" s="21" t="s">
         <v>247</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E27" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F27" s="21" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E31" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F31" s="21" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B36" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E36" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F36" s="21" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B45" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E45" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C45" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F45" s="21" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C48" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F48" s="21" t="s">
         <v>265</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="F48" s="21" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B52" s="21">
         <v>3</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E53" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E55" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B56" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E56" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C56" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F56" s="21" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="21" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C58" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="F58" s="21" t="s">
         <v>293</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="F58" s="21" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B61" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E61" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C61" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F61" s="21" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="21" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E63" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B65" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E65" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C65" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="E65" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F65" s="21" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="21" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="21" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B69" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E69" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C69" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="E69" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F69" s="21" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="21" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="21" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="21" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="21" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B73" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="E73" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C73" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="E73" s="21" t="s">
-        <v>234</v>
-      </c>
       <c r="F73" s="21" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="21" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E75" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="21" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="21" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E77" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F77" s="21" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="21" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E79" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F79" s="21" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="21" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E80" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="21" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E81" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="21" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="21" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D83" s="21" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E83" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="21" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E84" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="21" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E85" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="21" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E86" s="21" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="21" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E87" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="21" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="21" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="E89" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="21" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E90" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="21" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E91" s="21" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="21" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C92" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="E92" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="F92" s="21" t="s">
         <v>284</v>
-      </c>
-      <c r="D92" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="E92" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="F92" s="21" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="21" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B93" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D93" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="E93" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C93" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="D93" s="21" t="s">
+      <c r="F93" s="21" t="s">
         <v>285</v>
-      </c>
-      <c r="E93" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="F93" s="21" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="21" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E95" s="21" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F95" s="21" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -9464,7 +9483,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -9474,57 +9493,46 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -9544,827 +9552,827 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -10453,58 +10461,58 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -10523,242 +10531,242 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -11012,42 +11020,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>

--- a/data/reference/Unidades/plantilla_modelos_maquinarias.xlsx
+++ b/data/reference/Unidades/plantilla_modelos_maquinarias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tattersall-my.sharepoint.com/personal/sherrera_tattersall_cl/Documents/Escritorio/FACU/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{74B0ED40-AC33-4667-B411-C74549FB24E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CD3B6AD-362A-42CC-90FB-26B8407B8936}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{74B0ED40-AC33-4667-B411-C74549FB24E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8B8BB38-5C5F-4EF8-960A-A1211B1FA4BF}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="2025" windowWidth="20730" windowHeight="11040" tabRatio="790" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="790" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUT" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2041,9 +2041,6 @@
     <t>GRUA HORQUILLA</t>
   </si>
   <si>
-    <t>GRUA HOR</t>
-  </si>
-  <si>
     <t>GRUA PORTACONTENEDOR</t>
   </si>
   <si>
@@ -2060,6 +2057,9 @@
   </si>
   <si>
     <t>MANTELESC</t>
+  </si>
+  <si>
+    <t>GRUA-HOR</t>
   </si>
 </sst>
 </file>
@@ -2360,12 +2360,12 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6557,7 +6557,7 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="3" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="3" customWidth="1"/>
@@ -6599,7 +6599,7 @@
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="V2" s="43" t="s">
+      <c r="V2" s="40" t="s">
         <v>16</v>
       </c>
       <c r="W2" s="41"/>
@@ -6607,7 +6607,7 @@
       <c r="Z2" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="AE2" s="43" t="s">
+      <c r="AE2" s="40" t="s">
         <v>18</v>
       </c>
       <c r="AF2" s="41"/>
@@ -7139,7 +7139,7 @@
         <v>174</v>
       </c>
       <c r="S13" s="29" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="V13" s="31" t="s">
         <v>164</v>
@@ -7226,12 +7226,12 @@
         <v>196</v>
       </c>
       <c r="S16" s="29" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="V16" s="31"/>
       <c r="W16" s="31"/>
       <c r="X16" s="29"/>
-      <c r="Z16" s="40" t="s">
+      <c r="Z16" s="42" t="s">
         <v>186</v>
       </c>
       <c r="AA16" s="41"/>
@@ -7257,7 +7257,7 @@
       <c r="V17" s="31"/>
       <c r="W17" s="31"/>
       <c r="X17" s="29"/>
-      <c r="Z17" s="40" t="s">
+      <c r="Z17" s="42" t="s">
         <v>191</v>
       </c>
       <c r="AA17" s="41"/>
@@ -7279,7 +7279,7 @@
       <c r="V18" s="31"/>
       <c r="W18" s="31"/>
       <c r="X18" s="29"/>
-      <c r="Z18" s="42" t="s">
+      <c r="Z18" s="43" t="s">
         <v>194</v>
       </c>
       <c r="AA18" s="41"/>
@@ -7328,7 +7328,7 @@
         <v>657</v>
       </c>
       <c r="H21" s="39" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="S21" s="29" t="s">
         <v>657</v>
@@ -7336,7 +7336,7 @@
       <c r="V21" s="31"/>
       <c r="W21" s="31"/>
       <c r="X21" s="29"/>
-      <c r="Z21" s="40" t="s">
+      <c r="Z21" s="42" t="s">
         <v>202</v>
       </c>
       <c r="AA21" s="41"/>
@@ -7353,12 +7353,12 @@
         <v>117</v>
       </c>
       <c r="S22" s="29" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="V22" s="31"/>
       <c r="W22" s="31"/>
       <c r="X22" s="29"/>
-      <c r="Z22" s="40" t="s">
+      <c r="Z22" s="42" t="s">
         <v>205</v>
       </c>
       <c r="AA22" s="41"/>
@@ -7378,7 +7378,7 @@
       <c r="V23" s="31"/>
       <c r="W23" s="31"/>
       <c r="X23" s="29"/>
-      <c r="Z23" s="40" t="s">
+      <c r="Z23" s="42" t="s">
         <v>208</v>
       </c>
       <c r="AA23" s="41"/>
@@ -7398,7 +7398,7 @@
       <c r="V24" s="31"/>
       <c r="W24" s="31"/>
       <c r="X24" s="29"/>
-      <c r="Z24" s="40" t="s">
+      <c r="Z24" s="42" t="s">
         <v>209</v>
       </c>
       <c r="AA24" s="41"/>
@@ -7409,16 +7409,16 @@
     </row>
     <row r="25" spans="7:32" x14ac:dyDescent="0.25">
       <c r="G25" s="36" t="s">
+        <v>658</v>
+      </c>
+      <c r="H25" s="36" t="s">
         <v>659</v>
-      </c>
-      <c r="H25" s="36" t="s">
-        <v>660</v>
       </c>
       <c r="S25" s="29"/>
       <c r="V25" s="31"/>
       <c r="W25" s="31"/>
       <c r="X25" s="29"/>
-      <c r="Z25" s="40" t="s">
+      <c r="Z25" s="42" t="s">
         <v>210</v>
       </c>
       <c r="AA25" s="41"/>
@@ -7429,16 +7429,16 @@
     </row>
     <row r="26" spans="7:32" x14ac:dyDescent="0.25">
       <c r="G26" s="36" t="s">
+        <v>660</v>
+      </c>
+      <c r="H26" s="36" t="s">
         <v>661</v>
-      </c>
-      <c r="H26" s="36" t="s">
-        <v>662</v>
       </c>
       <c r="S26" s="29"/>
       <c r="V26" s="31"/>
       <c r="W26" s="31"/>
       <c r="X26" s="29"/>
-      <c r="Z26" s="40" t="s">
+      <c r="Z26" s="42" t="s">
         <v>211</v>
       </c>
       <c r="AA26" s="41"/>
@@ -7449,16 +7449,16 @@
     </row>
     <row r="27" spans="7:32" x14ac:dyDescent="0.25">
       <c r="G27" s="36" t="s">
+        <v>662</v>
+      </c>
+      <c r="H27" s="36" t="s">
         <v>663</v>
-      </c>
-      <c r="H27" s="36" t="s">
-        <v>664</v>
       </c>
       <c r="S27" s="29"/>
       <c r="V27" s="31"/>
       <c r="W27" s="31"/>
       <c r="X27" s="29"/>
-      <c r="Z27" s="40" t="s">
+      <c r="Z27" s="42" t="s">
         <v>212</v>
       </c>
       <c r="AA27" s="41"/>
@@ -7544,20 +7544,20 @@
       <c r="AF40" s="31"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <mergeCells count="12">
+    <mergeCell ref="Z27:AC27"/>
+    <mergeCell ref="Z22:AC22"/>
+    <mergeCell ref="Z26:AC26"/>
+    <mergeCell ref="Z17:AC17"/>
+    <mergeCell ref="Z18:AC18"/>
+    <mergeCell ref="Z21:AC21"/>
     <mergeCell ref="AE2:AF2"/>
     <mergeCell ref="Z24:AC24"/>
     <mergeCell ref="Z16:AC16"/>
     <mergeCell ref="Z25:AC25"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="Z23:AC23"/>
-    <mergeCell ref="Z27:AC27"/>
-    <mergeCell ref="Z22:AC22"/>
-    <mergeCell ref="Z26:AC26"/>
-    <mergeCell ref="Z17:AC17"/>
-    <mergeCell ref="Z18:AC18"/>
-    <mergeCell ref="Z21:AC21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
